--- a/doc/系统测试用例.xlsx
+++ b/doc/系统测试用例.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27830"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Horizon\Projects\Ongoing\AI_project\doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MINE\STUDY\SCHOOL\SEPP_SUMMER\mine_docs_etc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A918BB5-2FA4-4C9D-B0F7-4287CBEC7C8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4847E572-504A-4BB6-83D6-CCD1DF216382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Information" sheetId="7" r:id="rId1"/>
@@ -25,22 +25,11 @@
     <definedName name="压力测试用例常用测试项">测试用例常用测试项!$A$133</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="432">
   <si>
     <t>进行首次安装、升级、完整的或自定义的安装，系统能够正常进行安装</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1111,23 +1100,6 @@
         <charset val="134"/>
       </rPr>
       <t>作者</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Test Type
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>测试类型</t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1456,10 +1428,6 @@
     <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
-    <t>可以正常在浏览器中访问首页</t>
-    <phoneticPr fontId="29" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>1.</t>
     </r>
@@ -1579,151 +1547,6 @@
   </si>
   <si>
     <t>用户注册成功</t>
-    <phoneticPr fontId="29" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试注册非法数据是否成功</t>
-    <phoneticPr fontId="29" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>输入用户名</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>"xiaoming",</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>姓名</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>:"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>小明</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>",</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>密码</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>:"123456"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>，重复密码</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>:"654321",</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>邮箱</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>:"xiaoming163.com"
-2.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>点击注册按钮</t>
-    </r>
-    <phoneticPr fontId="29" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>提示</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>次密码不一致，邮箱格式错误</t>
-    </r>
     <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
@@ -1793,10 +1616,6 @@
     <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
-    <t>TimeGenie-testcase-003</t>
-    <phoneticPr fontId="29" type="noConversion"/>
-  </si>
-  <si>
     <t>用户登录</t>
     <phoneticPr fontId="29" type="noConversion"/>
   </si>
@@ -1865,15 +1684,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>操作系统兼容性测试</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>测试软件在不同分辨率的移动端显示功能是否正常</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试软件在不同系统下的移动端显示功能是否正常</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2017,10 +1828,6 @@
   </si>
   <si>
     <t>软件在不同分辨率移动端可显示</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>软件在不同系统移动端可显示</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2188,7 +1995,8 @@
         <family val="1"/>
         <charset val="134"/>
       </rPr>
-      <t>进入日程设置界面</t>
+      <t xml:space="preserve">进入总结页面
+</t>
     </r>
     <r>
       <rPr>
@@ -2196,8 +2004,7 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t xml:space="preserve">
-</t>
+      <t>2.</t>
     </r>
     <r>
       <rPr>
@@ -2206,7 +2013,23 @@
         <family val="1"/>
         <charset val="134"/>
       </rPr>
-      <t>2</t>
+      <t>选择开始日期和结束日期</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">招募从未使用过该系统的用户
+</t>
     </r>
     <r>
       <rPr>
@@ -2214,7 +2037,260 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>.</t>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">让用户自行尝试完成常见任务
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">3. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">观察用户的操作过程
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">4. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>记录用户遇到的困难和反馈</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+逐一浏览软件的各个界面，检查界面设计、颜色、字体等方面是否保持一致。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户登录成功</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户设置画像成功</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户修改画像成功</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户设置日程成功</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户可以正常查看日程</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户可以使用AI细分任务功能，选择删除或保留</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户可以使用AI提醒事项功能，选择删除或保留</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户可以使用AI总结功能，总结内容符合实际</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>软件在不同分辨率移动端可正常显示使用</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户很快掌握软件使用</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>系统提示错误原因</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+1.打开测试应用并进入登录页面
+2.输入错误的用户名和密码，尝试登录</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+1.使用性能测试工具模拟多个用户对软件进行请求，并监测系统的吞吐量
+2.调整负载，逐步提高并观察系统吞吐量的变化</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+模拟安装软件的过程，检查安装程序的完整性和正确性</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+1.迁移数据库至目标环境
+2.验证数据库迁移后系统的正常运行</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用性能测试工具模拟高压场景，测试软件在不同负载情况下的响应时间和事务通过情况</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用性能测试工具模拟低压场景，测试软件在不同负载情况下的响应时间和事务通过情况</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.对软件进行长时间运行测试，观察系统在连续运行中是否存在内存泄漏、性能下降等情况
+2.记录系统运行时间及相关性能指标，验证系统可运行时间是否符合预期</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>界面风格一致</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>在低压状态下响应迅速，事务均能够正确通过</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>在高压状态下响应能够保持稳定，保证事务能够继续通过</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>安装程序能够顺利完成安装，没有出现错误提示或异常情况</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据库迁移过程中数据完整性得到保留，迁移后系统能够正常运行，数据库无异常</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>初稿完成</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>齐佳怡，孙恬然，骆镒妤，赵楷越，朱涵</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TimeGenie-testcase-004</t>
+  </si>
+  <si>
+    <t>TimeGenie-testcase-005</t>
+  </si>
+  <si>
+    <t>TimeGenie-testcase-006</t>
+  </si>
+  <si>
+    <t>TimeGenie-testcase-007</t>
+  </si>
+  <si>
+    <t>TimeGenie-testcase-008</t>
+  </si>
+  <si>
+    <t>TimeGenie-testcase-009</t>
+  </si>
+  <si>
+    <t>TimeGenie-testcase-010</t>
+  </si>
+  <si>
+    <t>TimeGenie-testcase-011</t>
+  </si>
+  <si>
+    <t>TimeGenie-testcase-012</t>
+  </si>
+  <si>
+    <t>TimeGenie-testcase-013</t>
+  </si>
+  <si>
+    <t>TimeGenie-testcase-014</t>
+  </si>
+  <si>
+    <t>TimeGenie-testcase-015</t>
+  </si>
+  <si>
+    <t>TimeGenie-testcase-016</t>
+  </si>
+  <si>
+    <t>TimeGenie-testcase-017</t>
+  </si>
+  <si>
+    <t>TimeGenie-testcase-018</t>
+  </si>
+  <si>
+    <t>TimeGenie-testcase-019</t>
+  </si>
+  <si>
+    <t>TimeGenie-testcase-020</t>
+  </si>
+  <si>
+    <t>TimeGenie-testcase-021</t>
+  </si>
+  <si>
+    <t>TimeGenie-testcase-022</t>
+  </si>
+  <si>
+    <t>TimeGenie-testcase-023</t>
+  </si>
+  <si>
+    <t>安全性测试</t>
+  </si>
+  <si>
+    <t>TimeGenie-testcase-024</t>
+  </si>
+  <si>
+    <t>TimeGenie-testcase-025</t>
+  </si>
+  <si>
+    <t>后端api鉴权测试</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据库恢复及备份测试</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试数据库的可恢复性和安全性</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试后端接口访问的安全性</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>已部署至服务器</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
     </r>
     <r>
       <rPr>
@@ -2223,8 +2299,7 @@
         <family val="1"/>
         <charset val="134"/>
       </rPr>
-      <t>输入当天日程
-3.查看是否跳转到</t>
+      <t>、使用已鉴权的请求对后端</t>
     </r>
     <r>
       <rPr>
@@ -2232,7 +2307,7 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>AI</t>
+      <t>api</t>
     </r>
     <r>
       <rPr>
@@ -2241,14 +2316,333 @@
         <family val="1"/>
         <charset val="134"/>
       </rPr>
-      <t>助手界面
-4.选择提醒事项功能查看</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+      <t>进行访问2、使用未鉴权的请求对后端api进行访问</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>只有通过了鉴权步骤、才能通过后端api访问到对应的数据和结果</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>保证数据库在受到恶意攻击被清空后、或是由于其他原因导致数据丢失时、数据库的恢复功能正常</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、关闭数据库进程2、或清空数据库中所有数据</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>功能测试</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户注册</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试注册非法数据是否成功（密码）</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试注册非法数据是否成功（邮箱）</t>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <r>
       <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>输入用户名</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>"xiaoming",</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>姓名</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>:"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>小明</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>",</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>密码</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>:"123456"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，重复密码</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>:"654321",</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>邮箱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>:"xiaoming@163.com"
+2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>点击注册按钮</t>
+    </r>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>提示</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>次密码不一致</t>
+    </r>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>提示邮箱格式错误</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>输入用户名</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>"xiaoming",</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>姓名</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>:"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>小明</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>",</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>密码</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>:"123456"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，重复密码</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>:"123456",</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>邮箱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>:"xiaoming163.com"
+2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>点击注册按钮</t>
+    </r>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试非法数据是否登录成功（账号）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试非法数据是否登录成功（密码）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户数据未注册</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>输入邮箱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>:"xiaoming@163.com"</t>
     </r>
     <r>
       <rPr>
@@ -2257,7 +2651,7 @@
         <family val="1"/>
         <charset val="134"/>
       </rPr>
-      <t>进入日程设置界面</t>
+      <t>，输入密码654321</t>
     </r>
     <r>
       <rPr>
@@ -2266,7 +2660,43 @@
         <family val="1"/>
       </rPr>
       <t xml:space="preserve">
-</t>
+2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>点击登录按钮</t>
+    </r>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>提示密码错误</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>输入邮箱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>:"xiaoming1@163.com"</t>
     </r>
     <r>
       <rPr>
@@ -2275,7 +2705,7 @@
         <family val="1"/>
         <charset val="134"/>
       </rPr>
-      <t>2</t>
+      <t>，输入密码123456</t>
     </r>
     <r>
       <rPr>
@@ -2283,7 +2713,39 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>.</t>
+      <t xml:space="preserve">
+2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>点击登录按钮</t>
+    </r>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>提示用户名或密码错误</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试用户在线状态下是否可以导入某一路径下的全部资料</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户可以正常登录，且可以正常输入相应任务</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1.</t>
     </r>
     <r>
       <rPr>
@@ -2292,8 +2754,7 @@
         <family val="1"/>
         <charset val="134"/>
       </rPr>
-      <t>输入当天日程
-3.查看是否跳转到</t>
+      <t>进入日程设置界面</t>
     </r>
     <r>
       <rPr>
@@ -2301,7 +2762,8 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>AI</t>
+      <t xml:space="preserve">
+</t>
     </r>
     <r>
       <rPr>
@@ -2310,14 +2772,15 @@
         <family val="1"/>
         <charset val="134"/>
       </rPr>
-      <t>助手界面
-4.选择细分任务功能查看</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1.</t>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>.</t>
     </r>
     <r>
       <rPr>
@@ -2326,8 +2789,8 @@
         <family val="1"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">进入总结页面
-</t>
+      <t>在输入日程处导入相应的文件
+3.查看是否跳转到</t>
     </r>
     <r>
       <rPr>
@@ -2335,7 +2798,7 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>2.</t>
+      <t>AI</t>
     </r>
     <r>
       <rPr>
@@ -2344,7 +2807,8 @@
         <family val="1"/>
         <charset val="134"/>
       </rPr>
-      <t>选择开始日期和结束日期</t>
+      <t>助手界面
+4.查看AI是否给出相应的规划</t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2359,13 +2823,16 @@
         <family val="1"/>
         <charset val="134"/>
       </rPr>
-      <t>在不同分辨率移动端使用软件</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1.</t>
+      <t>进入日程设置界面</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
     </r>
     <r>
       <rPr>
@@ -2374,23 +2841,7 @@
         <family val="1"/>
         <charset val="134"/>
       </rPr>
-      <t>在不同系统移动端使用软件</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">招募从未使用过该系统的用户
-</t>
+      <t>2</t>
     </r>
     <r>
       <rPr>
@@ -2398,281 +2849,7 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t xml:space="preserve">2. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">让用户自行尝试完成常见任务
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">3. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">观察用户的操作过程
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">4. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>记录用户遇到的困难和反馈</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">
-逐一浏览软件的各个界面，检查界面设计、颜色、字体等方面是否保持一致。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>用户登录成功</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>用户设置画像成功</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>用户修改画像成功</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>用户设置日程成功</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>用户可以正常查看日程</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>用户可以使用AI细分任务功能，选择删除或保留</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>用户可以使用AI提醒事项功能，选择删除或保留</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>用户可以使用AI总结功能，总结内容符合实际</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>软件在不同分辨率移动端可正常显示使用</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>软件在不同系统移动端可正常显示使用</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>用户很快掌握软件使用</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>系统提示错误原因</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>响应时间符合预期</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">
-1.打开测试应用并进入登录页面
-2.输入错误的用户名和密码，尝试登录</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">
-1.使用性能测试工具模拟多个用户对软件进行请求，并监测系统的吞吐量
-2.调整负载，逐步提高并观察系统吞吐量的变化</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">
-模拟安装软件的过程，检查安装程序的完整性和正确性</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">
-1.迁移数据库至目标环境
-2.验证数据库迁移后系统的正常运行</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>使用性能测试工具模拟高压场景，测试软件在不同负载情况下的响应时间和事务通过情况</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>使用性能测试工具模拟低压场景，测试软件在不同负载情况下的响应时间和事务通过情况</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.依次操作软件的各项功能，记录每个功能的响应时间
-2.使用性能测试工具或者编写测试脚本，模拟多个用户同时使用软件，以检测在负载情况下的响应时间表现</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>吞吐量符合预期</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.对软件进行长时间运行测试，观察系统在连续运行中是否存在内存泄漏、性能下降等情况
-2.记录系统运行时间及相关性能指标，验证系统可运行时间是否符合预期</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>可运行时间符合预期</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>界面风格一致</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>在低压状态下响应迅速，事务均能够正确通过</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>在高压状态下响应能够保持稳定，保证事务能够继续通过</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>安装程序能够顺利完成安装，没有出现错误提示或异常情况</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>数据库迁移过程中数据完整性得到保留，迁移后系统能够正常运行，数据库无异常</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>初稿完成</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>齐佳怡，孙恬然，骆镒妤，赵楷越，朱涵</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>TimeGenie-testcase-004</t>
-  </si>
-  <si>
-    <t>TimeGenie-testcase-005</t>
-  </si>
-  <si>
-    <t>TimeGenie-testcase-006</t>
-  </si>
-  <si>
-    <t>TimeGenie-testcase-007</t>
-  </si>
-  <si>
-    <t>TimeGenie-testcase-008</t>
-  </si>
-  <si>
-    <t>TimeGenie-testcase-009</t>
-  </si>
-  <si>
-    <t>TimeGenie-testcase-010</t>
-  </si>
-  <si>
-    <t>TimeGenie-testcase-011</t>
-  </si>
-  <si>
-    <t>TimeGenie-testcase-012</t>
-  </si>
-  <si>
-    <t>TimeGenie-testcase-013</t>
-  </si>
-  <si>
-    <t>TimeGenie-testcase-014</t>
-  </si>
-  <si>
-    <t>TimeGenie-testcase-015</t>
-  </si>
-  <si>
-    <t>TimeGenie-testcase-016</t>
-  </si>
-  <si>
-    <t>TimeGenie-testcase-017</t>
-  </si>
-  <si>
-    <t>TimeGenie-testcase-018</t>
-  </si>
-  <si>
-    <t>TimeGenie-testcase-019</t>
-  </si>
-  <si>
-    <t>TimeGenie-testcase-020</t>
-  </si>
-  <si>
-    <t>TimeGenie-testcase-021</t>
-  </si>
-  <si>
-    <t>TimeGenie-testcase-022</t>
-  </si>
-  <si>
-    <t>TimeGenie-testcase-023</t>
-  </si>
-  <si>
-    <t>安全性测试</t>
-  </si>
-  <si>
-    <t>TimeGenie-testcase-024</t>
-  </si>
-  <si>
-    <t>TimeGenie-testcase-025</t>
-  </si>
-  <si>
-    <t>后端api鉴权测试</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>数据库恢复及备份测试</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试数据库的可恢复性和安全性</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试后端接口访问的安全性</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>已部署至服务器</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1</t>
+      <t>.</t>
     </r>
     <r>
       <rPr>
@@ -2681,7 +2858,8 @@
         <family val="1"/>
         <charset val="134"/>
       </rPr>
-      <t>、使用已鉴权的请求对后端</t>
+      <t>输入当天日程并明确时间
+3.查看是否跳转到</t>
     </r>
     <r>
       <rPr>
@@ -2689,7 +2867,7 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>api</t>
+      <t>AI</t>
     </r>
     <r>
       <rPr>
@@ -2698,20 +2876,355 @@
         <family val="1"/>
         <charset val="134"/>
       </rPr>
-      <t>进行访问2、使用未鉴权的请求对后端api进行访问</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>只有通过了鉴权步骤、才能通过后端api访问到对应的数据和结果</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>保证数据库在受到恶意攻击被清空后、或是由于其他原因导致数据丢失时、数据库的恢复功能正常</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、关闭数据库进程2、或清空数据库中所有数据</t>
+      <t>助手界面
+4.选择细分任务功能查看</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>进入日程设置界面</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>输入当天日程并明确时间
+3.查看是否跳转到</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>助手界面
+4.选择提醒事项功能查看</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>进入日程设置界面</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>输入当天日程并不输入明确时间
+3.查看是否跳转到</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>助手界面
+4.选择提醒事项功能查看</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>进入日程设置界面</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>输入当天日程并不明确时间
+3.查看是否跳转到</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>助手界面
+4.选择细分任务功能查看</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户可以使用AI提醒事项功能，选择删除或保留；AI给出合理的规划，将任务安排到具体时间</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户可以使用AI细分任务功能，选择删除或保留；AI给出合理的规划，将任务安排到具体时间</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试用户输入非法日期是否可以获得阶段总结</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户可以正常登录，且已经输入一段时间的相应日程。假设使用的日期是2024/01/01-2024/01/25</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">进入总结页面
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>选择开始日期和结束日期(2024/02/01,2024/03/23)</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>显示日期错误</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>响应时间符合预期，不调用AI的部分在1.5s内响应，调用AI的部分在5s内响应</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>吞吐量符合预期，可容纳的客户或事务数目标: 不少于10,000</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>可运行时间符合预期，平均每天可以使用22小时以上</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>在不同分辨率移动端使用软件（1080*2400，720*1280）</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.依次操作软件的各项功能，记录每个功能的响应时间
+2.使用性能测试工具或者编写测试脚本，模拟多个用户同时使用软件，以检测在负载情况下的响应时间表现（具体使用Jmeter进行测试）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TimeGenie-testcase-003</t>
+  </si>
+  <si>
+    <t>TimeGenie-testcase-026</t>
+  </si>
+  <si>
+    <t>TimeGenie-testcase-027</t>
+  </si>
+  <si>
+    <t>TimeGenie-testcase-028</t>
+  </si>
+  <si>
+    <t>TimeGenie-testcase-029</t>
+  </si>
+  <si>
+    <t>TimeGenie-testcase-030</t>
+  </si>
+  <si>
+    <t>TimeGenie-testcase-031</t>
+  </si>
+  <si>
+    <t>2.00</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>对初稿进行修改</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>可以正常在移动端中访问首页</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>Null(无缺陷)</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Low(微小错误)</t>
+  </si>
+  <si>
+    <t>添加邮箱判断</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>转发服务器宕机
+解决方案:切换转发服务器</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -3867,14 +4380,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I38"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.75" style="18" customWidth="1"/>
     <col min="2" max="2" width="25.25" style="10" customWidth="1"/>
     <col min="3" max="3" width="7" style="10" customWidth="1"/>
     <col min="4" max="4" width="21.5" style="10" customWidth="1"/>
     <col min="5" max="5" width="24.5" style="10" customWidth="1"/>
-    <col min="6" max="6" width="30.125" style="10" customWidth="1"/>
+    <col min="6" max="6" width="30.08203125" style="10" customWidth="1"/>
     <col min="7" max="7" width="17.25" style="10" customWidth="1"/>
     <col min="8" max="16384" width="9" style="10"/>
   </cols>
@@ -3882,7 +4395,7 @@
     <row r="1" spans="1:8" ht="51" customHeight="1">
       <c r="A1" s="22"/>
       <c r="B1" s="69" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C1" s="70"/>
       <c r="D1" s="70"/>
@@ -3906,7 +4419,7 @@
     <row r="3" spans="1:8" ht="23.25" customHeight="1">
       <c r="A3" s="16"/>
       <c r="B3" s="73" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C3" s="74"/>
       <c r="D3" s="75"/>
@@ -3916,7 +4429,7 @@
       <c r="F3" s="80"/>
       <c r="G3" s="12"/>
     </row>
-    <row r="4" spans="1:8" ht="28.5">
+    <row r="4" spans="1:8" ht="30">
       <c r="A4" s="16"/>
       <c r="B4" s="71" t="s">
         <v>213</v>
@@ -3938,10 +4451,10 @@
       </c>
       <c r="C5" s="75"/>
       <c r="D5" s="37" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E5" s="81" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F5" s="80"/>
       <c r="G5" s="12"/>
@@ -3949,7 +4462,7 @@
     <row r="6" spans="1:8" ht="101.25" customHeight="1">
       <c r="A6" s="20"/>
       <c r="B6" s="63" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="C6" s="64"/>
       <c r="D6" s="64"/>
@@ -3957,13 +4470,13 @@
       <c r="F6" s="66"/>
       <c r="G6" s="12"/>
     </row>
-    <row r="7" spans="1:8" ht="30">
+    <row r="7" spans="1:8" ht="30.5">
       <c r="A7" s="16"/>
       <c r="B7" s="3" t="s">
         <v>205</v>
       </c>
       <c r="C7" s="67" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="D7" s="68"/>
       <c r="E7" s="3" t="s">
@@ -3974,13 +4487,13 @@
       </c>
       <c r="G7" s="12"/>
     </row>
-    <row r="8" spans="1:8" ht="30">
+    <row r="8" spans="1:8" ht="30.5">
       <c r="A8" s="16"/>
       <c r="B8" s="3" t="s">
         <v>207</v>
       </c>
       <c r="C8" s="67" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="D8" s="68"/>
       <c r="E8" s="3" t="s">
@@ -3991,13 +4504,13 @@
       </c>
       <c r="G8" s="12"/>
     </row>
-    <row r="9" spans="1:8" ht="30">
+    <row r="9" spans="1:8" ht="30.5">
       <c r="A9" s="16"/>
       <c r="B9" s="3" t="s">
         <v>208</v>
       </c>
       <c r="C9" s="67" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="D9" s="68"/>
       <c r="E9" s="3" t="s">
@@ -4020,7 +4533,7 @@
       <c r="G10" s="12"/>
       <c r="H10" s="12"/>
     </row>
-    <row r="11" spans="1:8" ht="31.5">
+    <row r="11" spans="1:8" ht="32">
       <c r="A11" s="16"/>
       <c r="B11" s="59" t="s">
         <v>218</v>
@@ -4038,7 +4551,7 @@
       <c r="G11" s="12"/>
       <c r="H11" s="12"/>
     </row>
-    <row r="12" spans="1:8" ht="15.6" customHeight="1">
+    <row r="12" spans="1:8" ht="15.65" customHeight="1">
       <c r="A12" s="16"/>
       <c r="B12" s="60">
         <v>45480</v>
@@ -4048,24 +4561,32 @@
         <v>166</v>
       </c>
       <c r="E12" s="49" t="s">
-        <v>366</v>
+        <v>348</v>
       </c>
       <c r="F12" s="48" t="s">
-        <v>367</v>
+        <v>349</v>
       </c>
       <c r="G12" s="12"/>
       <c r="H12" s="12"/>
     </row>
-    <row r="13" spans="1:8" ht="15.75">
+    <row r="13" spans="1:8" ht="15.5">
       <c r="A13" s="16"/>
-      <c r="B13" s="52"/>
-      <c r="C13" s="53"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="31"/>
-      <c r="F13" s="31"/>
+      <c r="B13" s="60">
+        <v>45500</v>
+      </c>
+      <c r="C13" s="60"/>
+      <c r="D13" s="29" t="s">
+        <v>423</v>
+      </c>
+      <c r="E13" s="49" t="s">
+        <v>424</v>
+      </c>
+      <c r="F13" s="48" t="s">
+        <v>349</v>
+      </c>
       <c r="H13" s="12"/>
     </row>
-    <row r="14" spans="1:8" ht="15.75">
+    <row r="14" spans="1:8" ht="15.5">
       <c r="A14" s="16"/>
       <c r="B14" s="52"/>
       <c r="C14" s="53"/>
@@ -4074,7 +4595,7 @@
       <c r="F14" s="31"/>
       <c r="H14" s="12"/>
     </row>
-    <row r="15" spans="1:8" ht="15.75">
+    <row r="15" spans="1:8" ht="15.5">
       <c r="A15" s="16"/>
       <c r="B15" s="52"/>
       <c r="C15" s="53"/>
@@ -4083,7 +4604,7 @@
       <c r="F15" s="31"/>
       <c r="H15" s="12"/>
     </row>
-    <row r="16" spans="1:8" ht="15.75">
+    <row r="16" spans="1:8" ht="15.5">
       <c r="A16" s="16"/>
       <c r="B16" s="52"/>
       <c r="C16" s="53"/>
@@ -4092,7 +4613,7 @@
       <c r="F16" s="31"/>
       <c r="H16" s="12"/>
     </row>
-    <row r="17" spans="1:9" ht="15.75">
+    <row r="17" spans="1:9" ht="15.5">
       <c r="A17" s="16"/>
       <c r="B17" s="52"/>
       <c r="C17" s="53"/>
@@ -4104,7 +4625,7 @@
     <row r="18" spans="1:9" ht="28.5" customHeight="1">
       <c r="A18" s="22"/>
       <c r="B18" s="55" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C18" s="55"/>
       <c r="D18" s="55"/>
@@ -4134,19 +4655,19 @@
     <row r="20" spans="1:9" s="11" customFormat="1" ht="17.25" customHeight="1">
       <c r="A20" s="19"/>
       <c r="B20" s="61" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C20" s="62"/>
       <c r="D20" s="9">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E20" s="9">
         <f>SUMPRODUCT(('Test Cases'!C:C=B20)*('Test Cases'!K:K="Y"))</f>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F20" s="28">
         <f t="shared" ref="F20:F29" si="0">IF(D20,E20/D20,0)</f>
-        <v>0</v>
+        <v>0.94444444444444442</v>
       </c>
       <c r="G20" s="23"/>
       <c r="H20" s="10"/>
@@ -4155,7 +4676,7 @@
     <row r="21" spans="1:9" s="11" customFormat="1" ht="17.25" customHeight="1">
       <c r="A21" s="19"/>
       <c r="B21" s="50" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C21" s="51"/>
       <c r="D21" s="9">
@@ -4163,11 +4684,11 @@
       </c>
       <c r="E21" s="9">
         <f>SUMPRODUCT(('Test Cases'!C:C=B21)*('Test Cases'!K:K="Y"))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F21" s="28">
         <f>IF(D21,E21/D21,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" s="23"/>
       <c r="H21" s="10"/>
@@ -4176,7 +4697,7 @@
     <row r="22" spans="1:9" s="11" customFormat="1" ht="17.25" customHeight="1">
       <c r="A22" s="19"/>
       <c r="B22" s="50" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C22" s="51"/>
       <c r="D22" s="9">
@@ -4184,11 +4705,11 @@
       </c>
       <c r="E22" s="9">
         <f>SUMPRODUCT(('Test Cases'!C:C=B22)*('Test Cases'!K:K="Y"))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F22" s="28">
         <f>IF(D22,E22/D22,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" s="23"/>
       <c r="H22" s="10"/>
@@ -4197,7 +4718,7 @@
     <row r="23" spans="1:9" s="11" customFormat="1" ht="17.25" customHeight="1">
       <c r="A23" s="19"/>
       <c r="B23" s="50" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C23" s="51"/>
       <c r="D23" s="9">
@@ -4205,11 +4726,11 @@
       </c>
       <c r="E23" s="9">
         <f>SUMPRODUCT(('Test Cases'!C:C=B23)*('Test Cases'!K:K="Y"))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" s="28">
         <f>IF(D23,E23/D23,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" s="23"/>
       <c r="H23" s="10"/>
@@ -4218,19 +4739,19 @@
     <row r="24" spans="1:9" s="11" customFormat="1" ht="17.25" customHeight="1">
       <c r="A24" s="19"/>
       <c r="B24" s="50" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C24" s="51"/>
       <c r="D24" s="9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E24" s="9">
         <f>SUMPRODUCT(('Test Cases'!C:C=B24)*('Test Cases'!K:K="Y"))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F24" s="28">
         <f>IF(D24,E24/D24,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" s="23"/>
       <c r="H24" s="10"/>
@@ -4239,19 +4760,19 @@
     <row r="25" spans="1:9" s="11" customFormat="1" ht="17.25" customHeight="1">
       <c r="A25" s="19"/>
       <c r="B25" s="50" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C25" s="51"/>
       <c r="D25" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25" s="9">
         <f>SUMPRODUCT(('Test Cases'!C:C=B25)*('Test Cases'!K:K="Y"))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" s="28">
         <f>IF(D25,E25/D25,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" s="23"/>
       <c r="H25" s="10"/>
@@ -4260,7 +4781,7 @@
     <row r="26" spans="1:9" s="11" customFormat="1" ht="17.25" customHeight="1">
       <c r="A26" s="19"/>
       <c r="B26" s="50" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C26" s="54"/>
       <c r="D26" s="9">
@@ -4268,11 +4789,11 @@
       </c>
       <c r="E26" s="9">
         <f>SUMPRODUCT(('Test Cases'!C:C=B26)*('Test Cases'!K:K="Y"))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" s="28">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" s="23"/>
       <c r="H26" s="10"/>
@@ -4281,7 +4802,7 @@
     <row r="27" spans="1:9" s="11" customFormat="1" ht="17.25" customHeight="1">
       <c r="A27" s="19"/>
       <c r="B27" s="50" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C27" s="54"/>
       <c r="D27" s="9">
@@ -4289,18 +4810,18 @@
       </c>
       <c r="E27" s="9">
         <f>SUMPRODUCT(('Test Cases'!C:C=B27)*('Test Cases'!K:K="Y"))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F27" s="28">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" s="23"/>
     </row>
     <row r="28" spans="1:9" s="11" customFormat="1" ht="17.25" customHeight="1">
       <c r="A28" s="19"/>
       <c r="B28" s="50" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C28" s="54"/>
       <c r="D28" s="9">
@@ -4308,31 +4829,31 @@
       </c>
       <c r="E28" s="9">
         <f>SUMPRODUCT(('Test Cases'!C:C=B28)*('Test Cases'!K:K="Y"))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F28" s="28">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" s="23"/>
     </row>
-    <row r="29" spans="1:9" ht="15.75">
+    <row r="29" spans="1:9" ht="16">
       <c r="A29" s="24"/>
       <c r="B29" s="50" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C29" s="54"/>
       <c r="D29" s="9">
         <f>D20+D21+D22+D23+D24+D25+D26+D27+D28</f>
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E29" s="9">
         <f>COUNTIF('Test Cases'!K:K,"Y")</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F29" s="28">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.967741935483871</v>
       </c>
       <c r="G29" s="12"/>
     </row>
@@ -4370,7 +4891,7 @@
       <c r="C33" s="14"/>
       <c r="D33" s="14"/>
     </row>
-    <row r="34" spans="2:6" ht="15.75">
+    <row r="34" spans="2:6" ht="15.5">
       <c r="B34" s="14" t="s">
         <v>184</v>
       </c>
@@ -4379,19 +4900,19 @@
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
     </row>
-    <row r="35" spans="2:6" ht="15.75">
+    <row r="35" spans="2:6" ht="15.5">
       <c r="E35" s="11"/>
       <c r="F35" s="11"/>
     </row>
-    <row r="36" spans="2:6" ht="15.75">
+    <row r="36" spans="2:6" ht="15.5">
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
     </row>
-    <row r="37" spans="2:6" ht="15.75">
+    <row r="37" spans="2:6" ht="15.5">
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
     </row>
-    <row r="38" spans="2:6" ht="15.75">
+    <row r="38" spans="2:6" ht="15.5">
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
     </row>
@@ -4445,27 +4966,27 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AP904"/>
-  <sheetFormatPr defaultColWidth="13.125" defaultRowHeight="15.75"/>
+  <dimension ref="A1:AP893"/>
+  <sheetFormatPr defaultColWidth="13.08203125" defaultRowHeight="15.5"/>
   <cols>
     <col min="1" max="1" width="13.75" style="34" customWidth="1"/>
-    <col min="2" max="2" width="9.125" style="34" customWidth="1"/>
+    <col min="2" max="2" width="9.08203125" style="34" customWidth="1"/>
     <col min="3" max="3" width="9.25" style="34" customWidth="1"/>
     <col min="4" max="4" width="17.75" style="34" customWidth="1"/>
     <col min="5" max="5" width="12.75" style="35" customWidth="1"/>
     <col min="6" max="6" width="16.5" style="34" customWidth="1"/>
     <col min="7" max="7" width="16.75" style="34" customWidth="1"/>
-    <col min="8" max="8" width="17.375" style="34" customWidth="1"/>
+    <col min="8" max="8" width="17.33203125" style="34" customWidth="1"/>
     <col min="9" max="9" width="14.5" style="34" customWidth="1"/>
     <col min="10" max="10" width="15" style="34" customWidth="1"/>
-    <col min="11" max="11" width="8.875" style="34" customWidth="1"/>
+    <col min="11" max="11" width="8.83203125" style="34" customWidth="1"/>
     <col min="12" max="12" width="16.5" style="34" customWidth="1"/>
     <col min="13" max="13" width="5" style="5" hidden="1" customWidth="1"/>
     <col min="14" max="14" width="21.5" style="34" customWidth="1"/>
-    <col min="15" max="40" width="13.125" style="5"/>
+    <col min="15" max="40" width="13.08203125" style="5"/>
     <col min="41" max="41" width="13.25" style="5" customWidth="1"/>
-    <col min="42" max="42" width="4.375" style="5" hidden="1" customWidth="1"/>
-    <col min="43" max="16384" width="13.125" style="5"/>
+    <col min="42" max="42" width="4.33203125" style="5" hidden="1" customWidth="1"/>
+    <col min="43" max="16384" width="13.08203125" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:42" ht="19.5" customHeight="1">
@@ -4518,33 +5039,33 @@
       <c r="M3" s="84"/>
       <c r="N3" s="84"/>
     </row>
-    <row r="4" spans="1:42" ht="47.25">
+    <row r="4" spans="1:42" ht="46">
       <c r="A4" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>225</v>
-      </c>
       <c r="G4" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="H4" s="4" t="s">
-        <v>228</v>
-      </c>
       <c r="I4" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>159</v>
@@ -4553,929 +5074,1153 @@
         <v>168</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="5" spans="1:42" ht="105">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="5" spans="1:42" ht="115.5">
       <c r="A5" s="6" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="B5" s="43" t="s">
+        <v>249</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="D5" s="6" t="s">
+      <c r="E5" s="45" t="s">
         <v>251</v>
       </c>
-      <c r="E5" s="45" t="s">
-        <v>252</v>
-      </c>
       <c r="F5" s="46" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="G5" s="6"/>
       <c r="H5" s="6" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="I5" s="43" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="J5" s="43"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
+      <c r="K5" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>427</v>
+      </c>
       <c r="M5" s="32" t="s">
         <v>160</v>
       </c>
       <c r="N5" s="6"/>
     </row>
-    <row r="6" spans="1:42" ht="90">
+    <row r="6" spans="1:42" ht="115.5">
       <c r="A6" s="6" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="B6" s="43" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="D6" s="43" t="s">
-        <v>256</v>
+        <v>228</v>
+      </c>
+      <c r="D6" s="46" t="s">
+        <v>384</v>
       </c>
       <c r="E6" s="45" t="s">
-        <v>238</v>
-      </c>
-      <c r="F6" s="43" t="s">
-        <v>253</v>
+        <v>237</v>
+      </c>
+      <c r="F6" s="46" t="s">
+        <v>426</v>
       </c>
       <c r="G6" s="6"/>
       <c r="H6" s="6" t="s">
-        <v>257</v>
+        <v>386</v>
       </c>
       <c r="I6" s="46" t="s">
-        <v>258</v>
+        <v>387</v>
       </c>
       <c r="J6" s="43"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
+      <c r="K6" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>427</v>
+      </c>
       <c r="M6" s="32" t="s">
         <v>161</v>
       </c>
       <c r="N6" s="6"/>
     </row>
-    <row r="7" spans="1:42" ht="60">
+    <row r="7" spans="1:42" ht="101.5">
       <c r="A7" s="6" t="s">
-        <v>266</v>
+        <v>416</v>
       </c>
       <c r="B7" s="46" t="s">
-        <v>267</v>
+        <v>383</v>
       </c>
       <c r="C7" s="44" t="s">
-        <v>268</v>
-      </c>
-      <c r="D7" s="47" t="s">
-        <v>269</v>
+        <v>382</v>
+      </c>
+      <c r="D7" s="46" t="s">
+        <v>385</v>
       </c>
       <c r="E7" s="45" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="F7" s="46" t="s">
-        <v>270</v>
+        <v>426</v>
       </c>
       <c r="G7" s="6"/>
       <c r="H7" s="6" t="s">
-        <v>326</v>
+        <v>389</v>
       </c>
       <c r="I7" s="46" t="s">
-        <v>338</v>
+        <v>388</v>
       </c>
       <c r="J7" s="43"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="32" t="s">
-        <v>162</v>
-      </c>
-      <c r="N7" s="6"/>
-      <c r="X7" s="33"/>
-    </row>
-    <row r="8" spans="1:42" ht="85.5">
+      <c r="K7" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>429</v>
+      </c>
+      <c r="M7" s="32"/>
+      <c r="N7" s="44" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="8" spans="1:42" ht="73">
       <c r="A8" s="6" t="s">
-        <v>368</v>
+        <v>350</v>
       </c>
       <c r="B8" s="46" t="s">
-        <v>271</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="D8" s="44" t="s">
-        <v>273</v>
+        <v>261</v>
+      </c>
+      <c r="C8" s="44" t="s">
+        <v>382</v>
+      </c>
+      <c r="D8" s="46" t="s">
+        <v>390</v>
       </c>
       <c r="E8" s="45" t="s">
-        <v>252</v>
-      </c>
-      <c r="F8" s="43" t="s">
-        <v>259</v>
+        <v>237</v>
+      </c>
+      <c r="F8" s="46" t="s">
+        <v>392</v>
       </c>
       <c r="G8" s="6"/>
       <c r="H8" s="6" t="s">
-        <v>327</v>
+        <v>395</v>
       </c>
       <c r="I8" s="46" t="s">
-        <v>339</v>
+        <v>396</v>
       </c>
       <c r="J8" s="43"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="32" t="s">
-        <v>163</v>
-      </c>
+      <c r="K8" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="M8" s="32"/>
       <c r="N8" s="6"/>
-      <c r="X8" s="33"/>
-    </row>
-    <row r="9" spans="1:42" ht="55.5">
+    </row>
+    <row r="9" spans="1:42" ht="58.5">
       <c r="A9" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="B9" s="44" t="s">
-        <v>272</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="D9" s="44" t="s">
-        <v>274</v>
-      </c>
-      <c r="E9" s="36" t="s">
-        <v>287</v>
-      </c>
-      <c r="F9" s="44" t="s">
-        <v>317</v>
+        <v>351</v>
+      </c>
+      <c r="B9" s="46" t="s">
+        <v>261</v>
+      </c>
+      <c r="C9" s="44" t="s">
+        <v>382</v>
+      </c>
+      <c r="D9" s="46" t="s">
+        <v>391</v>
+      </c>
+      <c r="E9" s="45" t="s">
+        <v>237</v>
+      </c>
+      <c r="F9" s="46" t="s">
+        <v>264</v>
       </c>
       <c r="G9" s="6"/>
-      <c r="H9" s="44" t="s">
-        <v>328</v>
-      </c>
-      <c r="I9" s="44" t="s">
-        <v>340</v>
-      </c>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
+      <c r="H9" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="I9" s="46" t="s">
+        <v>394</v>
+      </c>
+      <c r="J9" s="43"/>
+      <c r="K9" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>427</v>
+      </c>
       <c r="M9" s="32"/>
       <c r="N9" s="6"/>
-      <c r="X9" s="33"/>
-      <c r="AP9" s="5" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="10" spans="1:42" ht="42">
+    </row>
+    <row r="10" spans="1:42" ht="58.5">
       <c r="A10" s="6" t="s">
-        <v>370</v>
-      </c>
-      <c r="B10" s="44" t="s">
-        <v>281</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="D10" s="44" t="s">
-        <v>275</v>
-      </c>
-      <c r="E10" s="36" t="s">
-        <v>288</v>
-      </c>
-      <c r="F10" s="44" t="s">
-        <v>319</v>
-      </c>
-      <c r="G10" s="44"/>
+        <v>352</v>
+      </c>
+      <c r="B10" s="46" t="s">
+        <v>261</v>
+      </c>
+      <c r="C10" s="44" t="s">
+        <v>262</v>
+      </c>
+      <c r="D10" s="47" t="s">
+        <v>263</v>
+      </c>
+      <c r="E10" s="45" t="s">
+        <v>251</v>
+      </c>
+      <c r="F10" s="46" t="s">
+        <v>264</v>
+      </c>
+      <c r="G10" s="6"/>
       <c r="H10" s="6" t="s">
-        <v>329</v>
-      </c>
-      <c r="I10" s="44" t="s">
-        <v>341</v>
-      </c>
-      <c r="J10" s="6"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="32"/>
+        <v>317</v>
+      </c>
+      <c r="I10" s="46" t="s">
+        <v>325</v>
+      </c>
+      <c r="J10" s="43"/>
+      <c r="K10" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="M10" s="32" t="s">
+        <v>162</v>
+      </c>
       <c r="N10" s="6"/>
       <c r="X10" s="33"/>
-      <c r="AP10" s="5" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="11" spans="1:42" ht="42">
+    </row>
+    <row r="11" spans="1:42" ht="86">
       <c r="A11" s="6" t="s">
-        <v>371</v>
-      </c>
-      <c r="B11" s="44" t="s">
-        <v>281</v>
+        <v>353</v>
+      </c>
+      <c r="B11" s="46" t="s">
+        <v>265</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D11" s="44" t="s">
-        <v>276</v>
-      </c>
-      <c r="E11" s="36" t="s">
-        <v>288</v>
-      </c>
-      <c r="F11" s="44" t="s">
+        <v>267</v>
+      </c>
+      <c r="E11" s="45" t="s">
+        <v>251</v>
+      </c>
+      <c r="F11" s="43" t="s">
+        <v>254</v>
+      </c>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6" t="s">
         <v>318</v>
       </c>
-      <c r="G11" s="42"/>
-      <c r="H11" s="6" t="s">
-        <v>329</v>
-      </c>
-      <c r="I11" s="44" t="s">
-        <v>341</v>
-      </c>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
-      <c r="M11" s="32"/>
+      <c r="I11" s="46" t="s">
+        <v>326</v>
+      </c>
+      <c r="J11" s="43"/>
+      <c r="K11" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="M11" s="32" t="s">
+        <v>163</v>
+      </c>
       <c r="N11" s="6"/>
-      <c r="AP11" s="5" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="12" spans="1:42" ht="45">
+      <c r="X11" s="33"/>
+    </row>
+    <row r="12" spans="1:42" ht="43">
       <c r="A12" s="6" t="s">
-        <v>372</v>
+        <v>354</v>
       </c>
       <c r="B12" s="44" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D12" s="44" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="E12" s="36" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="F12" s="44" t="s">
-        <v>317</v>
-      </c>
-      <c r="G12" s="42"/>
-      <c r="H12" s="6" t="s">
-        <v>330</v>
+        <v>309</v>
+      </c>
+      <c r="G12" s="6"/>
+      <c r="H12" s="44" t="s">
+        <v>319</v>
       </c>
       <c r="I12" s="44" t="s">
-        <v>342</v>
+        <v>327</v>
       </c>
       <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
+      <c r="K12" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>427</v>
+      </c>
       <c r="M12" s="32"/>
       <c r="N12" s="6"/>
+      <c r="X12" s="33"/>
       <c r="AP12" s="5" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="13" spans="1:42" ht="87">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="13" spans="1:42" ht="43">
       <c r="A13" s="6" t="s">
-        <v>373</v>
+        <v>355</v>
       </c>
       <c r="B13" s="44" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="E13" s="36" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="F13" s="44" t="s">
+        <v>311</v>
+      </c>
+      <c r="G13" s="44"/>
+      <c r="H13" s="6" t="s">
         <v>320</v>
       </c>
-      <c r="G13" s="42"/>
-      <c r="H13" s="6" t="s">
-        <v>331</v>
-      </c>
       <c r="I13" s="44" t="s">
-        <v>344</v>
+        <v>328</v>
       </c>
       <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
-      <c r="L13" s="6"/>
+      <c r="K13" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>427</v>
+      </c>
       <c r="M13" s="32"/>
       <c r="N13" s="6"/>
-    </row>
-    <row r="14" spans="1:42" ht="87">
+      <c r="X13" s="33"/>
+      <c r="AP13" s="5" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="14" spans="1:42" ht="43">
       <c r="A14" s="6" t="s">
-        <v>374</v>
+        <v>356</v>
       </c>
       <c r="B14" s="44" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D14" s="44" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="E14" s="36" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="F14" s="44" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="G14" s="42"/>
       <c r="H14" s="6" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="I14" s="44" t="s">
-        <v>343</v>
+        <v>328</v>
       </c>
       <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
-      <c r="L14" s="6"/>
+      <c r="K14" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="L14" s="6" t="s">
+        <v>427</v>
+      </c>
       <c r="M14" s="32"/>
-      <c r="N14" s="6"/>
-    </row>
-    <row r="15" spans="1:42" ht="45">
+      <c r="N14" s="44" t="s">
+        <v>431</v>
+      </c>
+      <c r="AP14" s="5" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="15" spans="1:42" ht="44">
       <c r="A15" s="6" t="s">
-        <v>375</v>
+        <v>357</v>
       </c>
       <c r="B15" s="44" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D15" s="44" t="s">
+        <v>271</v>
+      </c>
+      <c r="E15" s="36" t="s">
         <v>280</v>
       </c>
-      <c r="E15" s="36" t="s">
-        <v>289</v>
-      </c>
       <c r="F15" s="44" t="s">
+        <v>309</v>
+      </c>
+      <c r="G15" s="42"/>
+      <c r="H15" s="6" t="s">
         <v>321</v>
       </c>
-      <c r="G15" s="43"/>
-      <c r="H15" s="6" t="s">
-        <v>333</v>
-      </c>
       <c r="I15" s="44" t="s">
-        <v>345</v>
+        <v>329</v>
       </c>
       <c r="J15" s="6"/>
-      <c r="K15" s="6"/>
-      <c r="L15" s="6"/>
+      <c r="K15" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>427</v>
+      </c>
       <c r="M15" s="32"/>
       <c r="N15" s="6"/>
-    </row>
-    <row r="16" spans="1:42" ht="42">
+      <c r="AP15" s="5" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="16" spans="1:42" ht="100.5">
       <c r="A16" s="6" t="s">
-        <v>376</v>
+        <v>358</v>
       </c>
       <c r="B16" s="44" t="s">
-        <v>283</v>
-      </c>
-      <c r="C16" s="44" t="s">
-        <v>290</v>
+        <v>276</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>228</v>
       </c>
       <c r="D16" s="44" t="s">
-        <v>285</v>
+        <v>272</v>
       </c>
       <c r="E16" s="36" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="F16" s="44" t="s">
-        <v>322</v>
-      </c>
-      <c r="G16" s="43"/>
+        <v>312</v>
+      </c>
+      <c r="G16" s="42"/>
       <c r="H16" s="6" t="s">
-        <v>334</v>
+        <v>402</v>
       </c>
       <c r="I16" s="44" t="s">
-        <v>346</v>
+        <v>331</v>
       </c>
       <c r="J16" s="6"/>
-      <c r="K16" s="6"/>
-      <c r="L16" s="6"/>
+      <c r="K16" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="L16" s="6" t="s">
+        <v>427</v>
+      </c>
       <c r="M16" s="32"/>
       <c r="N16" s="6"/>
     </row>
-    <row r="17" spans="1:14" ht="42">
+    <row r="17" spans="1:14" ht="100.5">
       <c r="A17" s="6" t="s">
-        <v>377</v>
+        <v>359</v>
       </c>
       <c r="B17" s="44" t="s">
-        <v>284</v>
-      </c>
-      <c r="C17" s="44" t="s">
-        <v>290</v>
+        <v>276</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>228</v>
       </c>
       <c r="D17" s="44" t="s">
-        <v>286</v>
+        <v>272</v>
       </c>
       <c r="E17" s="36" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="F17" s="44" t="s">
-        <v>323</v>
-      </c>
-      <c r="G17" s="6"/>
+        <v>312</v>
+      </c>
+      <c r="G17" s="42"/>
       <c r="H17" s="6" t="s">
-        <v>335</v>
+        <v>403</v>
       </c>
       <c r="I17" s="44" t="s">
-        <v>347</v>
+        <v>405</v>
       </c>
       <c r="J17" s="6"/>
-      <c r="K17" s="6"/>
-      <c r="L17" s="6"/>
+      <c r="K17" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="L17" s="6" t="s">
+        <v>427</v>
+      </c>
       <c r="M17" s="32"/>
       <c r="N17" s="6"/>
     </row>
-    <row r="18" spans="1:14" ht="115.5">
+    <row r="18" spans="1:14" ht="100.5">
       <c r="A18" s="6" t="s">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="B18" s="44" t="s">
-        <v>291</v>
+        <v>276</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>292</v>
+        <v>228</v>
       </c>
       <c r="D18" s="44" t="s">
-        <v>294</v>
+        <v>273</v>
       </c>
       <c r="E18" s="36" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="F18" s="44" t="s">
-        <v>324</v>
-      </c>
-      <c r="G18" s="6"/>
+        <v>312</v>
+      </c>
+      <c r="G18" s="42"/>
       <c r="H18" s="6" t="s">
-        <v>336</v>
+        <v>401</v>
       </c>
       <c r="I18" s="44" t="s">
-        <v>348</v>
+        <v>330</v>
       </c>
       <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
-      <c r="L18" s="6"/>
+      <c r="K18" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="L18" s="6" t="s">
+        <v>427</v>
+      </c>
       <c r="M18" s="32"/>
       <c r="N18" s="6"/>
     </row>
-    <row r="19" spans="1:14" ht="82.5">
+    <row r="19" spans="1:14" ht="100.5">
       <c r="A19" s="6" t="s">
-        <v>379</v>
+        <v>361</v>
       </c>
       <c r="B19" s="44" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>292</v>
+        <v>228</v>
       </c>
       <c r="D19" s="44" t="s">
-        <v>295</v>
+        <v>273</v>
       </c>
       <c r="E19" s="36" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="F19" s="44" t="s">
-        <v>325</v>
-      </c>
-      <c r="G19" s="6"/>
-      <c r="H19" s="44" t="s">
-        <v>351</v>
+        <v>312</v>
+      </c>
+      <c r="G19" s="42"/>
+      <c r="H19" s="6" t="s">
+        <v>404</v>
       </c>
       <c r="I19" s="44" t="s">
-        <v>349</v>
+        <v>406</v>
       </c>
       <c r="J19" s="6"/>
-      <c r="K19" s="6"/>
-      <c r="L19" s="6"/>
+      <c r="K19" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="L19" s="6" t="s">
+        <v>427</v>
+      </c>
       <c r="M19" s="32"/>
       <c r="N19" s="6"/>
     </row>
-    <row r="20" spans="1:14" ht="123">
+    <row r="20" spans="1:14" ht="100.5">
       <c r="A20" s="6" t="s">
-        <v>380</v>
+        <v>362</v>
       </c>
       <c r="B20" s="44" t="s">
-        <v>297</v>
-      </c>
-      <c r="C20" s="44" t="s">
-        <v>296</v>
+        <v>276</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>228</v>
       </c>
       <c r="D20" s="44" t="s">
-        <v>298</v>
+        <v>398</v>
       </c>
       <c r="E20" s="36" t="s">
-        <v>289</v>
+        <v>397</v>
       </c>
       <c r="F20" s="44" t="s">
-        <v>324</v>
-      </c>
-      <c r="G20" s="6"/>
-      <c r="H20" s="44" t="s">
-        <v>357</v>
+        <v>399</v>
+      </c>
+      <c r="G20" s="42"/>
+      <c r="H20" s="6" t="s">
+        <v>400</v>
       </c>
       <c r="I20" s="44" t="s">
-        <v>350</v>
+        <v>330</v>
       </c>
       <c r="J20" s="6"/>
-      <c r="K20" s="6"/>
-      <c r="L20" s="6"/>
+      <c r="K20" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="L20" s="6" t="s">
+        <v>427</v>
+      </c>
       <c r="M20" s="32"/>
       <c r="N20" s="6"/>
     </row>
-    <row r="21" spans="1:14" ht="109.5">
+    <row r="21" spans="1:14" ht="44">
       <c r="A21" s="6" t="s">
-        <v>381</v>
+        <v>363</v>
       </c>
       <c r="B21" s="44" t="s">
-        <v>299</v>
-      </c>
-      <c r="C21" s="44" t="s">
-        <v>296</v>
+        <v>276</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>228</v>
       </c>
       <c r="D21" s="44" t="s">
-        <v>302</v>
+        <v>274</v>
       </c>
       <c r="E21" s="36" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="F21" s="44" t="s">
-        <v>324</v>
-      </c>
-      <c r="G21" s="6"/>
-      <c r="H21" s="44" t="s">
-        <v>352</v>
+        <v>313</v>
+      </c>
+      <c r="G21" s="43"/>
+      <c r="H21" s="6" t="s">
+        <v>322</v>
       </c>
       <c r="I21" s="44" t="s">
-        <v>358</v>
+        <v>332</v>
       </c>
       <c r="J21" s="6"/>
-      <c r="K21" s="6"/>
-      <c r="L21" s="6"/>
+      <c r="K21" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="L21" s="6" t="s">
+        <v>427</v>
+      </c>
       <c r="M21" s="32"/>
       <c r="N21" s="6"/>
     </row>
-    <row r="22" spans="1:14" ht="136.5">
+    <row r="22" spans="1:14" ht="85">
       <c r="A22" s="6" t="s">
-        <v>382</v>
+        <v>364</v>
       </c>
       <c r="B22" s="44" t="s">
-        <v>301</v>
-      </c>
-      <c r="C22" s="44" t="s">
-        <v>300</v>
+        <v>276</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>228</v>
       </c>
       <c r="D22" s="44" t="s">
-        <v>303</v>
+        <v>407</v>
       </c>
       <c r="E22" s="36" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="F22" s="44" t="s">
-        <v>324</v>
-      </c>
-      <c r="G22" s="6"/>
-      <c r="H22" s="44" t="s">
-        <v>359</v>
+        <v>408</v>
+      </c>
+      <c r="G22" s="43"/>
+      <c r="H22" s="6" t="s">
+        <v>409</v>
       </c>
       <c r="I22" s="44" t="s">
-        <v>360</v>
+        <v>410</v>
       </c>
       <c r="J22" s="6"/>
-      <c r="K22" s="6"/>
-      <c r="L22" s="6"/>
+      <c r="K22" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="L22" s="6" t="s">
+        <v>427</v>
+      </c>
       <c r="M22" s="32"/>
       <c r="N22" s="6"/>
     </row>
-    <row r="23" spans="1:14" ht="82.5">
+    <row r="23" spans="1:14" ht="57.5">
       <c r="A23" s="6" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
       <c r="B23" s="44" t="s">
-        <v>305</v>
+        <v>277</v>
       </c>
       <c r="C23" s="44" t="s">
-        <v>304</v>
+        <v>282</v>
       </c>
       <c r="D23" s="44" t="s">
-        <v>306</v>
+        <v>278</v>
       </c>
       <c r="E23" s="36" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="F23" s="44" t="s">
-        <v>324</v>
-      </c>
-      <c r="G23" s="6"/>
-      <c r="H23" s="44" t="s">
-        <v>337</v>
+        <v>314</v>
+      </c>
+      <c r="G23" s="43"/>
+      <c r="H23" s="6" t="s">
+        <v>414</v>
       </c>
       <c r="I23" s="44" t="s">
-        <v>361</v>
+        <v>333</v>
       </c>
       <c r="J23" s="6"/>
-      <c r="K23" s="6"/>
-      <c r="L23" s="6"/>
+      <c r="K23" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="L23" s="6" t="s">
+        <v>427</v>
+      </c>
       <c r="M23" s="32"/>
       <c r="N23" s="6"/>
     </row>
-    <row r="24" spans="1:14" ht="69">
+    <row r="24" spans="1:14" ht="115">
       <c r="A24" s="6" t="s">
-        <v>384</v>
+        <v>366</v>
       </c>
       <c r="B24" s="44" t="s">
-        <v>310</v>
-      </c>
-      <c r="C24" s="44" t="s">
-        <v>307</v>
-      </c>
-      <c r="D24" s="46" t="s">
-        <v>308</v>
+        <v>283</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="D24" s="44" t="s">
+        <v>286</v>
       </c>
       <c r="E24" s="36" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="F24" s="44" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="G24" s="6"/>
-      <c r="H24" s="44" t="s">
-        <v>356</v>
+      <c r="H24" s="6" t="s">
+        <v>323</v>
       </c>
       <c r="I24" s="44" t="s">
-        <v>362</v>
+        <v>334</v>
       </c>
       <c r="J24" s="6"/>
-      <c r="K24" s="6"/>
-      <c r="L24" s="6"/>
+      <c r="K24" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="L24" s="6" t="s">
+        <v>427</v>
+      </c>
       <c r="M24" s="32"/>
       <c r="N24" s="6"/>
     </row>
-    <row r="25" spans="1:14" ht="69">
+    <row r="25" spans="1:14" ht="71">
       <c r="A25" s="6" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
       <c r="B25" s="44" t="s">
-        <v>311</v>
-      </c>
-      <c r="C25" s="44" t="s">
-        <v>307</v>
-      </c>
-      <c r="D25" s="46" t="s">
-        <v>309</v>
+        <v>285</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="D25" s="44" t="s">
+        <v>287</v>
       </c>
       <c r="E25" s="36" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="F25" s="44" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="G25" s="6"/>
       <c r="H25" s="44" t="s">
-        <v>355</v>
+        <v>336</v>
       </c>
       <c r="I25" s="44" t="s">
-        <v>363</v>
+        <v>335</v>
       </c>
       <c r="J25" s="6"/>
-      <c r="K25" s="6"/>
-      <c r="L25" s="6"/>
+      <c r="K25" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="L25" s="6" t="s">
+        <v>427</v>
+      </c>
       <c r="M25" s="32"/>
       <c r="N25" s="6"/>
     </row>
-    <row r="26" spans="1:14" ht="55.5">
+    <row r="26" spans="1:14" ht="141">
       <c r="A26" s="6" t="s">
-        <v>386</v>
+        <v>368</v>
       </c>
       <c r="B26" s="44" t="s">
-        <v>313</v>
+        <v>289</v>
       </c>
       <c r="C26" s="44" t="s">
-        <v>312</v>
+        <v>288</v>
       </c>
       <c r="D26" s="44" t="s">
-        <v>314</v>
+        <v>290</v>
       </c>
       <c r="E26" s="36" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="F26" s="44" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="G26" s="6"/>
       <c r="H26" s="44" t="s">
-        <v>353</v>
-      </c>
-      <c r="I26" s="46" t="s">
-        <v>364</v>
+        <v>415</v>
+      </c>
+      <c r="I26" s="44" t="s">
+        <v>411</v>
       </c>
       <c r="J26" s="6"/>
-      <c r="K26" s="6"/>
-      <c r="L26" s="6"/>
+      <c r="K26" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="L26" s="6" t="s">
+        <v>427</v>
+      </c>
       <c r="M26" s="32"/>
       <c r="N26" s="6"/>
     </row>
-    <row r="27" spans="1:14" ht="82.5">
+    <row r="27" spans="1:14" ht="113">
       <c r="A27" s="6" t="s">
-        <v>387</v>
+        <v>369</v>
       </c>
       <c r="B27" s="44" t="s">
-        <v>316</v>
+        <v>291</v>
       </c>
       <c r="C27" s="44" t="s">
-        <v>312</v>
+        <v>288</v>
       </c>
       <c r="D27" s="44" t="s">
+        <v>294</v>
+      </c>
+      <c r="E27" s="36" t="s">
+        <v>281</v>
+      </c>
+      <c r="F27" s="44" t="s">
         <v>315</v>
-      </c>
-      <c r="E27" s="36" t="s">
-        <v>288</v>
-      </c>
-      <c r="F27" s="44" t="s">
-        <v>324</v>
       </c>
       <c r="G27" s="6"/>
       <c r="H27" s="44" t="s">
-        <v>354</v>
+        <v>337</v>
       </c>
       <c r="I27" s="44" t="s">
-        <v>365</v>
+        <v>412</v>
       </c>
       <c r="J27" s="6"/>
-      <c r="K27" s="6"/>
-      <c r="L27" s="6"/>
+      <c r="K27" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="L27" s="6" t="s">
+        <v>427</v>
+      </c>
       <c r="M27" s="32"/>
       <c r="N27" s="6"/>
     </row>
-    <row r="28" spans="1:14" ht="96">
+    <row r="28" spans="1:14" ht="127">
       <c r="A28" s="6" t="s">
-        <v>389</v>
+        <v>371</v>
       </c>
       <c r="B28" s="44" t="s">
-        <v>392</v>
-      </c>
-      <c r="C28" s="46" t="s">
-        <v>388</v>
+        <v>293</v>
+      </c>
+      <c r="C28" s="44" t="s">
+        <v>292</v>
       </c>
       <c r="D28" s="44" t="s">
-        <v>393</v>
+        <v>295</v>
       </c>
       <c r="E28" s="36" t="s">
-        <v>238</v>
+        <v>281</v>
       </c>
       <c r="F28" s="44" t="s">
-        <v>395</v>
+        <v>315</v>
       </c>
       <c r="G28" s="6"/>
-      <c r="H28" s="46" t="s">
-        <v>399</v>
+      <c r="H28" s="44" t="s">
+        <v>342</v>
       </c>
       <c r="I28" s="44" t="s">
-        <v>398</v>
+        <v>413</v>
       </c>
       <c r="J28" s="6"/>
-      <c r="K28" s="6"/>
-      <c r="L28" s="6"/>
+      <c r="K28" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="L28" s="6" t="s">
+        <v>427</v>
+      </c>
       <c r="M28" s="32"/>
       <c r="N28" s="6"/>
     </row>
-    <row r="29" spans="1:14" ht="72">
+    <row r="29" spans="1:14" ht="71">
       <c r="A29" s="6" t="s">
-        <v>390</v>
+        <v>372</v>
       </c>
       <c r="B29" s="44" t="s">
-        <v>391</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>388</v>
+        <v>297</v>
+      </c>
+      <c r="C29" s="44" t="s">
+        <v>296</v>
       </c>
       <c r="D29" s="44" t="s">
-        <v>394</v>
+        <v>298</v>
       </c>
       <c r="E29" s="36" t="s">
-        <v>238</v>
+        <v>281</v>
       </c>
       <c r="F29" s="44" t="s">
-        <v>395</v>
+        <v>315</v>
       </c>
       <c r="G29" s="6"/>
-      <c r="H29" s="6" t="s">
-        <v>396</v>
+      <c r="H29" s="44" t="s">
+        <v>324</v>
       </c>
       <c r="I29" s="44" t="s">
-        <v>397</v>
+        <v>343</v>
       </c>
       <c r="J29" s="6"/>
-      <c r="K29" s="6"/>
-      <c r="L29" s="6"/>
+      <c r="K29" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="L29" s="6" t="s">
+        <v>427</v>
+      </c>
       <c r="M29" s="32"/>
       <c r="N29" s="6"/>
     </row>
-    <row r="30" spans="1:14">
-      <c r="A30" s="6"/>
-      <c r="B30" s="44"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="44"/>
-      <c r="E30" s="36"/>
-      <c r="F30" s="44"/>
+    <row r="30" spans="1:14" ht="71">
+      <c r="A30" s="6" t="s">
+        <v>417</v>
+      </c>
+      <c r="B30" s="44" t="s">
+        <v>302</v>
+      </c>
+      <c r="C30" s="44" t="s">
+        <v>299</v>
+      </c>
+      <c r="D30" s="46" t="s">
+        <v>300</v>
+      </c>
+      <c r="E30" s="36" t="s">
+        <v>281</v>
+      </c>
+      <c r="F30" s="44" t="s">
+        <v>315</v>
+      </c>
       <c r="G30" s="6"/>
-      <c r="H30" s="6"/>
-      <c r="I30" s="44"/>
+      <c r="H30" s="44" t="s">
+        <v>341</v>
+      </c>
+      <c r="I30" s="44" t="s">
+        <v>344</v>
+      </c>
       <c r="J30" s="6"/>
-      <c r="K30" s="6"/>
-      <c r="L30" s="6"/>
+      <c r="K30" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="L30" s="6" t="s">
+        <v>427</v>
+      </c>
       <c r="M30" s="32"/>
       <c r="N30" s="6"/>
     </row>
-    <row r="31" spans="1:14">
-      <c r="A31" s="6"/>
-      <c r="B31" s="44"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="44"/>
-      <c r="E31" s="36"/>
-      <c r="F31" s="44"/>
+    <row r="31" spans="1:14" ht="71">
+      <c r="A31" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="B31" s="44" t="s">
+        <v>303</v>
+      </c>
+      <c r="C31" s="44" t="s">
+        <v>299</v>
+      </c>
+      <c r="D31" s="46" t="s">
+        <v>301</v>
+      </c>
+      <c r="E31" s="36" t="s">
+        <v>281</v>
+      </c>
+      <c r="F31" s="44" t="s">
+        <v>315</v>
+      </c>
       <c r="G31" s="6"/>
-      <c r="H31" s="6"/>
-      <c r="I31" s="44"/>
+      <c r="H31" s="44" t="s">
+        <v>340</v>
+      </c>
+      <c r="I31" s="44" t="s">
+        <v>345</v>
+      </c>
       <c r="J31" s="6"/>
-      <c r="K31" s="6"/>
-      <c r="L31" s="6"/>
+      <c r="K31" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="L31" s="6" t="s">
+        <v>427</v>
+      </c>
       <c r="M31" s="32"/>
       <c r="N31" s="6"/>
     </row>
-    <row r="32" spans="1:14">
-      <c r="A32" s="6"/>
-      <c r="B32" s="44"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="44"/>
-      <c r="E32" s="36"/>
-      <c r="F32" s="44"/>
+    <row r="32" spans="1:14" ht="57">
+      <c r="A32" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="B32" s="44" t="s">
+        <v>305</v>
+      </c>
+      <c r="C32" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="D32" s="44" t="s">
+        <v>306</v>
+      </c>
+      <c r="E32" s="36" t="s">
+        <v>280</v>
+      </c>
+      <c r="F32" s="44" t="s">
+        <v>315</v>
+      </c>
       <c r="G32" s="6"/>
-      <c r="H32" s="6"/>
-      <c r="I32" s="44"/>
+      <c r="H32" s="44" t="s">
+        <v>338</v>
+      </c>
+      <c r="I32" s="46" t="s">
+        <v>346</v>
+      </c>
       <c r="J32" s="6"/>
-      <c r="K32" s="6"/>
-      <c r="L32" s="6"/>
+      <c r="K32" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="L32" s="6" t="s">
+        <v>427</v>
+      </c>
       <c r="M32" s="32"/>
       <c r="N32" s="6"/>
     </row>
-    <row r="33" spans="1:14">
-      <c r="A33" s="6"/>
-      <c r="B33" s="44"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="44"/>
-      <c r="E33" s="36"/>
-      <c r="F33" s="44"/>
+    <row r="33" spans="1:14" ht="85">
+      <c r="A33" s="6" t="s">
+        <v>420</v>
+      </c>
+      <c r="B33" s="44" t="s">
+        <v>308</v>
+      </c>
+      <c r="C33" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="D33" s="44" t="s">
+        <v>307</v>
+      </c>
+      <c r="E33" s="36" t="s">
+        <v>280</v>
+      </c>
+      <c r="F33" s="44" t="s">
+        <v>315</v>
+      </c>
       <c r="G33" s="6"/>
-      <c r="H33" s="6"/>
-      <c r="I33" s="44"/>
+      <c r="H33" s="44" t="s">
+        <v>339</v>
+      </c>
+      <c r="I33" s="44" t="s">
+        <v>347</v>
+      </c>
       <c r="J33" s="6"/>
-      <c r="K33" s="6"/>
-      <c r="L33" s="6"/>
+      <c r="K33" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="L33" s="6" t="s">
+        <v>427</v>
+      </c>
       <c r="M33" s="32"/>
       <c r="N33" s="6"/>
     </row>
-    <row r="34" spans="1:14">
-      <c r="A34" s="6"/>
-      <c r="B34" s="44"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="44"/>
-      <c r="E34" s="36"/>
-      <c r="F34" s="44"/>
+    <row r="34" spans="1:14" ht="99">
+      <c r="A34" s="6" t="s">
+        <v>421</v>
+      </c>
+      <c r="B34" s="44" t="s">
+        <v>374</v>
+      </c>
+      <c r="C34" s="46" t="s">
+        <v>370</v>
+      </c>
+      <c r="D34" s="44" t="s">
+        <v>375</v>
+      </c>
+      <c r="E34" s="36" t="s">
+        <v>237</v>
+      </c>
+      <c r="F34" s="44" t="s">
+        <v>377</v>
+      </c>
       <c r="G34" s="6"/>
-      <c r="H34" s="6"/>
-      <c r="I34" s="44"/>
+      <c r="H34" s="46" t="s">
+        <v>381</v>
+      </c>
+      <c r="I34" s="44" t="s">
+        <v>380</v>
+      </c>
       <c r="J34" s="6"/>
-      <c r="K34" s="6"/>
-      <c r="L34" s="6"/>
+      <c r="K34" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="L34" s="6" t="s">
+        <v>427</v>
+      </c>
       <c r="M34" s="32"/>
       <c r="N34" s="6"/>
     </row>
-    <row r="35" spans="1:14">
-      <c r="A35" s="6"/>
-      <c r="B35" s="44"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="44"/>
-      <c r="E35" s="36"/>
-      <c r="F35" s="44"/>
+    <row r="35" spans="1:14" ht="72">
+      <c r="A35" s="6" t="s">
+        <v>422</v>
+      </c>
+      <c r="B35" s="44" t="s">
+        <v>373</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="D35" s="44" t="s">
+        <v>376</v>
+      </c>
+      <c r="E35" s="36" t="s">
+        <v>237</v>
+      </c>
+      <c r="F35" s="44" t="s">
+        <v>377</v>
+      </c>
       <c r="G35" s="6"/>
-      <c r="H35" s="6"/>
-      <c r="I35" s="44"/>
+      <c r="H35" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="I35" s="44" t="s">
+        <v>379</v>
+      </c>
       <c r="J35" s="6"/>
-      <c r="K35" s="6"/>
-      <c r="L35" s="6"/>
+      <c r="K35" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="L35" s="6" t="s">
+        <v>427</v>
+      </c>
       <c r="M35" s="32"/>
       <c r="N35" s="6"/>
     </row>
@@ -5487,8 +6232,8 @@
       <c r="E36" s="36"/>
       <c r="F36" s="44"/>
       <c r="G36" s="6"/>
-      <c r="H36" s="6"/>
-      <c r="I36" s="44"/>
+      <c r="H36" s="42"/>
+      <c r="I36" s="42"/>
       <c r="J36" s="6"/>
       <c r="K36" s="6"/>
       <c r="L36" s="6"/>
@@ -5499,11 +6244,11 @@
       <c r="A37" s="6"/>
       <c r="B37" s="44"/>
       <c r="C37" s="6"/>
-      <c r="D37" s="44"/>
+      <c r="D37" s="42"/>
       <c r="E37" s="36"/>
       <c r="F37" s="44"/>
       <c r="G37" s="6"/>
-      <c r="H37" s="44"/>
+      <c r="H37" s="6"/>
       <c r="I37" s="44"/>
       <c r="J37" s="6"/>
       <c r="K37" s="6"/>
@@ -5515,11 +6260,11 @@
       <c r="A38" s="6"/>
       <c r="B38" s="44"/>
       <c r="C38" s="6"/>
-      <c r="D38" s="44"/>
+      <c r="D38" s="42"/>
       <c r="E38" s="36"/>
       <c r="F38" s="44"/>
       <c r="G38" s="6"/>
-      <c r="H38" s="44"/>
+      <c r="H38" s="6"/>
       <c r="I38" s="44"/>
       <c r="J38" s="6"/>
       <c r="K38" s="6"/>
@@ -5529,14 +6274,14 @@
     </row>
     <row r="39" spans="1:14">
       <c r="A39" s="6"/>
-      <c r="B39" s="44"/>
+      <c r="B39" s="6"/>
       <c r="C39" s="6"/>
-      <c r="D39" s="44"/>
+      <c r="D39" s="6"/>
       <c r="E39" s="36"/>
-      <c r="F39" s="44"/>
+      <c r="F39" s="6"/>
       <c r="G39" s="6"/>
-      <c r="H39" s="43"/>
-      <c r="I39" s="44"/>
+      <c r="H39" s="6"/>
+      <c r="I39" s="6"/>
       <c r="J39" s="6"/>
       <c r="K39" s="6"/>
       <c r="L39" s="6"/>
@@ -5545,14 +6290,14 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="6"/>
-      <c r="B40" s="44"/>
+      <c r="B40" s="6"/>
       <c r="C40" s="6"/>
-      <c r="D40" s="44"/>
+      <c r="D40" s="6"/>
       <c r="E40" s="36"/>
-      <c r="F40" s="43"/>
+      <c r="F40" s="6"/>
       <c r="G40" s="6"/>
-      <c r="H40" s="43"/>
-      <c r="I40" s="44"/>
+      <c r="H40" s="6"/>
+      <c r="I40" s="6"/>
       <c r="J40" s="6"/>
       <c r="K40" s="6"/>
       <c r="L40" s="6"/>
@@ -5561,14 +6306,14 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="6"/>
-      <c r="B41" s="44"/>
+      <c r="B41" s="6"/>
       <c r="C41" s="6"/>
       <c r="D41" s="6"/>
       <c r="E41" s="36"/>
-      <c r="F41" s="43"/>
+      <c r="F41" s="6"/>
       <c r="G41" s="6"/>
-      <c r="H41" s="42"/>
-      <c r="I41" s="42"/>
+      <c r="H41" s="6"/>
+      <c r="I41" s="6"/>
       <c r="J41" s="6"/>
       <c r="K41" s="6"/>
       <c r="L41" s="6"/>
@@ -5577,14 +6322,14 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="6"/>
-      <c r="B42" s="44"/>
+      <c r="B42" s="6"/>
       <c r="C42" s="6"/>
-      <c r="D42" s="44"/>
+      <c r="D42" s="6"/>
       <c r="E42" s="36"/>
-      <c r="F42" s="44"/>
+      <c r="F42" s="6"/>
       <c r="G42" s="6"/>
-      <c r="H42" s="42"/>
-      <c r="I42" s="42"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="6"/>
       <c r="J42" s="6"/>
       <c r="K42" s="6"/>
       <c r="L42" s="6"/>
@@ -5593,14 +6338,14 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="6"/>
-      <c r="B43" s="44"/>
+      <c r="B43" s="6"/>
       <c r="C43" s="6"/>
-      <c r="D43" s="42"/>
+      <c r="D43" s="6"/>
       <c r="E43" s="36"/>
-      <c r="F43" s="44"/>
+      <c r="F43" s="6"/>
       <c r="G43" s="6"/>
       <c r="H43" s="6"/>
-      <c r="I43" s="44"/>
+      <c r="I43" s="6"/>
       <c r="J43" s="6"/>
       <c r="K43" s="6"/>
       <c r="L43" s="6"/>
@@ -5609,14 +6354,14 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="6"/>
-      <c r="B44" s="44"/>
+      <c r="B44" s="6"/>
       <c r="C44" s="6"/>
-      <c r="D44" s="42"/>
+      <c r="D44" s="6"/>
       <c r="E44" s="36"/>
-      <c r="F44" s="44"/>
+      <c r="F44" s="6"/>
       <c r="G44" s="6"/>
       <c r="H44" s="6"/>
-      <c r="I44" s="44"/>
+      <c r="I44" s="6"/>
       <c r="J44" s="6"/>
       <c r="K44" s="6"/>
       <c r="L44" s="6"/>
@@ -5625,14 +6370,14 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="6"/>
-      <c r="B45" s="44"/>
+      <c r="B45" s="6"/>
       <c r="C45" s="6"/>
-      <c r="D45" s="42"/>
+      <c r="D45" s="6"/>
       <c r="E45" s="36"/>
-      <c r="F45" s="44"/>
+      <c r="F45" s="6"/>
       <c r="G45" s="6"/>
       <c r="H45" s="6"/>
-      <c r="I45" s="44"/>
+      <c r="I45" s="6"/>
       <c r="J45" s="6"/>
       <c r="K45" s="6"/>
       <c r="L45" s="6"/>
@@ -5641,14 +6386,14 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="6"/>
-      <c r="B46" s="44"/>
+      <c r="B46" s="6"/>
       <c r="C46" s="6"/>
-      <c r="D46" s="44"/>
+      <c r="D46" s="6"/>
       <c r="E46" s="36"/>
-      <c r="F46" s="44"/>
+      <c r="F46" s="6"/>
       <c r="G46" s="6"/>
       <c r="H46" s="6"/>
-      <c r="I46" s="44"/>
+      <c r="I46" s="6"/>
       <c r="J46" s="6"/>
       <c r="K46" s="6"/>
       <c r="L46" s="6"/>
@@ -5657,14 +6402,14 @@
     </row>
     <row r="47" spans="1:14">
       <c r="A47" s="6"/>
-      <c r="B47" s="44"/>
+      <c r="B47" s="6"/>
       <c r="C47" s="6"/>
-      <c r="D47" s="44"/>
+      <c r="D47" s="6"/>
       <c r="E47" s="36"/>
-      <c r="F47" s="44"/>
+      <c r="F47" s="6"/>
       <c r="G47" s="6"/>
       <c r="H47" s="6"/>
-      <c r="I47" s="44"/>
+      <c r="I47" s="6"/>
       <c r="J47" s="6"/>
       <c r="K47" s="6"/>
       <c r="L47" s="6"/>
@@ -5721,14 +6466,8 @@
     </row>
     <row r="51" spans="1:14">
       <c r="A51" s="6"/>
-      <c r="B51" s="6"/>
       <c r="C51" s="6"/>
-      <c r="D51" s="6"/>
       <c r="E51" s="36"/>
-      <c r="F51" s="6"/>
-      <c r="G51" s="6"/>
-      <c r="H51" s="6"/>
-      <c r="I51" s="6"/>
       <c r="J51" s="6"/>
       <c r="K51" s="6"/>
       <c r="L51" s="6"/>
@@ -5737,14 +6476,8 @@
     </row>
     <row r="52" spans="1:14">
       <c r="A52" s="6"/>
-      <c r="B52" s="6"/>
       <c r="C52" s="6"/>
-      <c r="D52" s="6"/>
       <c r="E52" s="36"/>
-      <c r="F52" s="6"/>
-      <c r="G52" s="6"/>
-      <c r="H52" s="6"/>
-      <c r="I52" s="6"/>
       <c r="J52" s="6"/>
       <c r="K52" s="6"/>
       <c r="L52" s="6"/>
@@ -5753,14 +6486,8 @@
     </row>
     <row r="53" spans="1:14">
       <c r="A53" s="6"/>
-      <c r="B53" s="6"/>
       <c r="C53" s="6"/>
-      <c r="D53" s="6"/>
       <c r="E53" s="36"/>
-      <c r="F53" s="6"/>
-      <c r="G53" s="6"/>
-      <c r="H53" s="6"/>
-      <c r="I53" s="6"/>
       <c r="J53" s="6"/>
       <c r="K53" s="6"/>
       <c r="L53" s="6"/>
@@ -5769,14 +6496,8 @@
     </row>
     <row r="54" spans="1:14">
       <c r="A54" s="6"/>
-      <c r="B54" s="6"/>
       <c r="C54" s="6"/>
-      <c r="D54" s="6"/>
       <c r="E54" s="36"/>
-      <c r="F54" s="6"/>
-      <c r="G54" s="6"/>
-      <c r="H54" s="6"/>
-      <c r="I54" s="6"/>
       <c r="J54" s="6"/>
       <c r="K54" s="6"/>
       <c r="L54" s="6"/>
@@ -5785,14 +6506,8 @@
     </row>
     <row r="55" spans="1:14">
       <c r="A55" s="6"/>
-      <c r="B55" s="6"/>
       <c r="C55" s="6"/>
-      <c r="D55" s="6"/>
       <c r="E55" s="36"/>
-      <c r="F55" s="6"/>
-      <c r="G55" s="6"/>
-      <c r="H55" s="6"/>
-      <c r="I55" s="6"/>
       <c r="J55" s="6"/>
       <c r="K55" s="6"/>
       <c r="L55" s="6"/>
@@ -5801,14 +6516,8 @@
     </row>
     <row r="56" spans="1:14">
       <c r="A56" s="6"/>
-      <c r="B56" s="6"/>
       <c r="C56" s="6"/>
-      <c r="D56" s="6"/>
       <c r="E56" s="36"/>
-      <c r="F56" s="6"/>
-      <c r="G56" s="6"/>
-      <c r="H56" s="6"/>
-      <c r="I56" s="6"/>
       <c r="J56" s="6"/>
       <c r="K56" s="6"/>
       <c r="L56" s="6"/>
@@ -5817,14 +6526,8 @@
     </row>
     <row r="57" spans="1:14">
       <c r="A57" s="6"/>
-      <c r="B57" s="6"/>
       <c r="C57" s="6"/>
-      <c r="D57" s="6"/>
       <c r="E57" s="36"/>
-      <c r="F57" s="6"/>
-      <c r="G57" s="6"/>
-      <c r="H57" s="6"/>
-      <c r="I57" s="6"/>
       <c r="J57" s="6"/>
       <c r="K57" s="6"/>
       <c r="L57" s="6"/>
@@ -5833,14 +6536,8 @@
     </row>
     <row r="58" spans="1:14">
       <c r="A58" s="6"/>
-      <c r="B58" s="6"/>
       <c r="C58" s="6"/>
-      <c r="D58" s="6"/>
       <c r="E58" s="36"/>
-      <c r="F58" s="6"/>
-      <c r="G58" s="6"/>
-      <c r="H58" s="6"/>
-      <c r="I58" s="6"/>
       <c r="J58" s="6"/>
       <c r="K58" s="6"/>
       <c r="L58" s="6"/>
@@ -5849,14 +6546,8 @@
     </row>
     <row r="59" spans="1:14">
       <c r="A59" s="6"/>
-      <c r="B59" s="6"/>
       <c r="C59" s="6"/>
-      <c r="D59" s="6"/>
       <c r="E59" s="36"/>
-      <c r="F59" s="6"/>
-      <c r="G59" s="6"/>
-      <c r="H59" s="6"/>
-      <c r="I59" s="6"/>
       <c r="J59" s="6"/>
       <c r="K59" s="6"/>
       <c r="L59" s="6"/>
@@ -5865,14 +6556,8 @@
     </row>
     <row r="60" spans="1:14">
       <c r="A60" s="6"/>
-      <c r="B60" s="6"/>
       <c r="C60" s="6"/>
-      <c r="D60" s="6"/>
       <c r="E60" s="36"/>
-      <c r="F60" s="6"/>
-      <c r="G60" s="6"/>
-      <c r="H60" s="6"/>
-      <c r="I60" s="6"/>
       <c r="J60" s="6"/>
       <c r="K60" s="6"/>
       <c r="L60" s="6"/>
@@ -5881,14 +6566,8 @@
     </row>
     <row r="61" spans="1:14">
       <c r="A61" s="6"/>
-      <c r="B61" s="6"/>
       <c r="C61" s="6"/>
-      <c r="D61" s="6"/>
       <c r="E61" s="36"/>
-      <c r="F61" s="6"/>
-      <c r="G61" s="6"/>
-      <c r="H61" s="6"/>
-      <c r="I61" s="6"/>
       <c r="J61" s="6"/>
       <c r="K61" s="6"/>
       <c r="L61" s="6"/>
@@ -5898,95 +6577,115 @@
     <row r="62" spans="1:14">
       <c r="C62" s="6"/>
       <c r="E62" s="36"/>
+      <c r="J62" s="6"/>
       <c r="K62" s="6"/>
       <c r="L62" s="6"/>
+      <c r="M62" s="32"/>
+      <c r="N62" s="6"/>
     </row>
     <row r="63" spans="1:14">
       <c r="C63" s="6"/>
       <c r="E63" s="36"/>
+      <c r="J63" s="6"/>
+      <c r="K63" s="6"/>
       <c r="L63" s="6"/>
+      <c r="M63" s="32"/>
+      <c r="N63" s="6"/>
     </row>
     <row r="64" spans="1:14">
       <c r="C64" s="6"/>
       <c r="E64" s="36"/>
+      <c r="J64" s="6"/>
+      <c r="K64" s="6"/>
       <c r="L64" s="6"/>
-    </row>
-    <row r="65" spans="3:12">
+      <c r="M64" s="32"/>
+      <c r="N64" s="6"/>
+    </row>
+    <row r="65" spans="3:14">
       <c r="C65" s="6"/>
       <c r="E65" s="36"/>
+      <c r="J65" s="6"/>
+      <c r="K65" s="6"/>
       <c r="L65" s="6"/>
-    </row>
-    <row r="66" spans="3:12">
+      <c r="M65" s="32"/>
+      <c r="N65" s="6"/>
+    </row>
+    <row r="66" spans="3:14">
       <c r="C66" s="6"/>
       <c r="E66" s="36"/>
+      <c r="J66" s="6"/>
+      <c r="K66" s="6"/>
       <c r="L66" s="6"/>
-    </row>
-    <row r="67" spans="3:12">
+      <c r="M66" s="32"/>
+      <c r="N66" s="6"/>
+    </row>
+    <row r="67" spans="3:14">
       <c r="C67" s="6"/>
       <c r="E67" s="36"/>
+      <c r="K67" s="6"/>
       <c r="L67" s="6"/>
     </row>
-    <row r="68" spans="3:12">
+    <row r="68" spans="3:14">
       <c r="C68" s="6"/>
       <c r="E68" s="36"/>
       <c r="L68" s="6"/>
     </row>
-    <row r="69" spans="3:12">
+    <row r="69" spans="3:14">
       <c r="C69" s="6"/>
       <c r="E69" s="36"/>
       <c r="L69" s="6"/>
     </row>
-    <row r="70" spans="3:12">
+    <row r="70" spans="3:14">
       <c r="C70" s="6"/>
       <c r="E70" s="36"/>
       <c r="L70" s="6"/>
     </row>
-    <row r="71" spans="3:12">
+    <row r="71" spans="3:14">
       <c r="C71" s="6"/>
       <c r="E71" s="36"/>
       <c r="L71" s="6"/>
     </row>
-    <row r="72" spans="3:12">
+    <row r="72" spans="3:14">
       <c r="C72" s="6"/>
       <c r="E72" s="36"/>
       <c r="L72" s="6"/>
     </row>
-    <row r="73" spans="3:12">
+    <row r="73" spans="3:14">
       <c r="C73" s="6"/>
       <c r="E73" s="36"/>
       <c r="L73" s="6"/>
     </row>
-    <row r="74" spans="3:12">
+    <row r="74" spans="3:14">
       <c r="C74" s="6"/>
       <c r="E74" s="36"/>
       <c r="L74" s="6"/>
     </row>
-    <row r="75" spans="3:12">
+    <row r="75" spans="3:14">
       <c r="C75" s="6"/>
       <c r="E75" s="36"/>
       <c r="L75" s="6"/>
     </row>
-    <row r="76" spans="3:12">
+    <row r="76" spans="3:14">
       <c r="C76" s="6"/>
       <c r="E76" s="36"/>
       <c r="L76" s="6"/>
     </row>
-    <row r="77" spans="3:12">
+    <row r="77" spans="3:14">
       <c r="C77" s="6"/>
       <c r="E77" s="36"/>
       <c r="L77" s="6"/>
     </row>
-    <row r="78" spans="3:12">
+    <row r="78" spans="3:14">
       <c r="C78" s="6"/>
       <c r="E78" s="36"/>
       <c r="L78" s="6"/>
     </row>
-    <row r="79" spans="3:12">
+    <row r="79" spans="3:14">
       <c r="C79" s="6"/>
       <c r="E79" s="36"/>
       <c r="L79" s="6"/>
     </row>
-    <row r="80" spans="3:12">
+    <row r="80" spans="3:14">
       <c r="C80" s="6"/>
       <c r="E80" s="36"/>
       <c r="L80" s="6"/>
@@ -9708,57 +10407,46 @@
     </row>
     <row r="824" spans="3:12">
       <c r="C824" s="6"/>
-      <c r="E824" s="36"/>
       <c r="L824" s="6"/>
     </row>
     <row r="825" spans="3:12">
       <c r="C825" s="6"/>
-      <c r="E825" s="36"/>
       <c r="L825" s="6"/>
     </row>
     <row r="826" spans="3:12">
       <c r="C826" s="6"/>
-      <c r="E826" s="36"/>
       <c r="L826" s="6"/>
     </row>
     <row r="827" spans="3:12">
       <c r="C827" s="6"/>
-      <c r="E827" s="36"/>
       <c r="L827" s="6"/>
     </row>
     <row r="828" spans="3:12">
       <c r="C828" s="6"/>
-      <c r="E828" s="36"/>
       <c r="L828" s="6"/>
     </row>
     <row r="829" spans="3:12">
       <c r="C829" s="6"/>
-      <c r="E829" s="36"/>
       <c r="L829" s="6"/>
     </row>
     <row r="830" spans="3:12">
       <c r="C830" s="6"/>
-      <c r="E830" s="36"/>
       <c r="L830" s="6"/>
     </row>
     <row r="831" spans="3:12">
       <c r="C831" s="6"/>
-      <c r="E831" s="36"/>
       <c r="L831" s="6"/>
     </row>
     <row r="832" spans="3:12">
       <c r="C832" s="6"/>
-      <c r="E832" s="36"/>
       <c r="L832" s="6"/>
     </row>
     <row r="833" spans="3:12">
       <c r="C833" s="6"/>
-      <c r="E833" s="36"/>
       <c r="L833" s="6"/>
     </row>
     <row r="834" spans="3:12">
       <c r="C834" s="6"/>
-      <c r="E834" s="36"/>
       <c r="L834" s="6"/>
     </row>
     <row r="835" spans="3:12">
@@ -9945,77 +10633,49 @@
       <c r="C880" s="6"/>
       <c r="L880" s="6"/>
     </row>
-    <row r="881" spans="3:3">
+    <row r="881" spans="3:12">
       <c r="C881" s="6"/>
-    </row>
-    <row r="882" spans="3:3">
+      <c r="L881" s="6"/>
+    </row>
+    <row r="882" spans="3:12">
       <c r="C882" s="6"/>
-    </row>
-    <row r="883" spans="3:3">
+      <c r="L882" s="6"/>
+    </row>
+    <row r="883" spans="3:12">
       <c r="C883" s="6"/>
-    </row>
-    <row r="884" spans="3:3">
+      <c r="L883" s="6"/>
+    </row>
+    <row r="884" spans="3:12">
       <c r="C884" s="6"/>
-    </row>
-    <row r="885" spans="3:3">
+      <c r="L884" s="6"/>
+    </row>
+    <row r="885" spans="3:12">
       <c r="C885" s="6"/>
-    </row>
-    <row r="886" spans="3:3">
+      <c r="L885" s="6"/>
+    </row>
+    <row r="886" spans="3:12">
       <c r="C886" s="6"/>
     </row>
-    <row r="887" spans="3:3">
+    <row r="887" spans="3:12">
       <c r="C887" s="6"/>
     </row>
-    <row r="888" spans="3:3">
+    <row r="888" spans="3:12">
       <c r="C888" s="6"/>
     </row>
-    <row r="889" spans="3:3">
+    <row r="889" spans="3:12">
       <c r="C889" s="6"/>
     </row>
-    <row r="890" spans="3:3">
+    <row r="890" spans="3:12">
       <c r="C890" s="6"/>
     </row>
-    <row r="891" spans="3:3">
+    <row r="891" spans="3:12">
       <c r="C891" s="6"/>
     </row>
-    <row r="892" spans="3:3">
+    <row r="892" spans="3:12">
       <c r="C892" s="6"/>
     </row>
-    <row r="893" spans="3:3">
+    <row r="893" spans="3:12">
       <c r="C893" s="6"/>
-    </row>
-    <row r="894" spans="3:3">
-      <c r="C894" s="6"/>
-    </row>
-    <row r="895" spans="3:3">
-      <c r="C895" s="6"/>
-    </row>
-    <row r="896" spans="3:3">
-      <c r="C896" s="6"/>
-    </row>
-    <row r="897" spans="3:3">
-      <c r="C897" s="6"/>
-    </row>
-    <row r="898" spans="3:3">
-      <c r="C898" s="6"/>
-    </row>
-    <row r="899" spans="3:3">
-      <c r="C899" s="6"/>
-    </row>
-    <row r="900" spans="3:3">
-      <c r="C900" s="6"/>
-    </row>
-    <row r="901" spans="3:3">
-      <c r="C901" s="6"/>
-    </row>
-    <row r="902" spans="3:3">
-      <c r="C902" s="6"/>
-    </row>
-    <row r="903" spans="3:3">
-      <c r="C903" s="6"/>
-    </row>
-    <row r="904" spans="3:3">
-      <c r="C904" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -10026,16 +10686,16 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K4" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>$X$5:$X$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K5:K65536" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K5:K65541" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:C65536" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:C65525" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"功能测试,性能测试,易用性测试,可靠性测试,安全性测试,兼容性测试,界面测试,压力测试,部署测试"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5:E834" xr:uid="{00000000-0002-0000-0100-000003000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5:E823" xr:uid="{00000000-0002-0000-0100-000003000000}">
       <formula1>"高,中,低"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L5:L880" xr:uid="{00000000-0002-0000-0100-000004000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L5:L885" xr:uid="{00000000-0002-0000-0100-000004000000}">
       <formula1>"Null(无缺陷),Urgent(严重错误),High(主要错误),Medium(一般错误),Low(微小错误)"</formula1>
     </dataValidation>
   </dataValidations>
@@ -10048,22 +10708,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C142"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="17" style="1" customWidth="1"/>
-    <col min="2" max="2" width="132.625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="50.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="132.58203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="50.58203125" style="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="303" customHeight="1">
       <c r="B1" s="40" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="87" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B3" s="87"/>
     </row>
@@ -10175,7 +10835,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="25.5">
+    <row r="22" spans="1:2" ht="27">
       <c r="A22" s="85"/>
       <c r="B22" s="2" t="s">
         <v>27</v>
@@ -10301,7 +10961,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="25.5">
+    <row r="42" spans="1:2" ht="27">
       <c r="A42" s="85"/>
       <c r="B42" s="2" t="s">
         <v>154</v>
@@ -10443,7 +11103,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="64" spans="1:2" ht="25.5">
+    <row r="64" spans="1:2" ht="27">
       <c r="A64" s="85"/>
       <c r="B64" s="2" t="s">
         <v>90</v>
@@ -10683,7 +11343,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="99" spans="1:3" ht="63.75">
+    <row r="99" spans="1:3" ht="67.5">
       <c r="A99" s="90"/>
       <c r="B99" s="2" t="s">
         <v>75</v>

--- a/doc/系统测试用例.xlsx
+++ b/doc/系统测试用例.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MINE\STUDY\SCHOOL\SEPP_SUMMER\mine_docs_etc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4847E572-504A-4BB6-83D6-CCD1DF216382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A4ED0D2-7FB8-4220-9E4B-DD4087CFF564}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Information" sheetId="7" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="426">
   <si>
     <t>进行首次安装、升级、完整的或自定义的安装，系统能够正常进行安装</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -2337,15 +2337,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>用户注册</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>测试注册非法数据是否成功（密码）</t>
-    <phoneticPr fontId="29" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试注册非法数据是否成功（邮箱）</t>
     <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
@@ -2490,7 +2482,15 @@
     <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
-    <t>提示邮箱格式错误</t>
+    <t>测试非法数据是否登录成功（账号）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试非法数据是否登录成功（密码）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户数据未注册</t>
     <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
@@ -2504,7 +2504,7 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>输入用户名</t>
+      <t>输入邮箱</t>
     </r>
     <r>
       <rPr>
@@ -2512,7 +2512,25 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>"xiaoming",</t>
+      <t>:"xiaoming@163.com"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，输入密码654321</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+2.</t>
     </r>
     <r>
       <rPr>
@@ -2521,15 +2539,17 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>姓名</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>:"</t>
+      <t>点击登录按钮</t>
+    </r>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>提示密码错误</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1.</t>
     </r>
     <r>
       <rPr>
@@ -2538,7 +2558,7 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>小明</t>
+      <t>输入邮箱</t>
     </r>
     <r>
       <rPr>
@@ -2546,7 +2566,25 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>",</t>
+      <t>:"xiaoming1@163.com"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，输入密码123456</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+2.</t>
     </r>
     <r>
       <rPr>
@@ -2555,94 +2593,29 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>密码</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>:"123456"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>，重复密码</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>:"123456",</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>邮箱</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>:"xiaoming163.com"
-2.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>点击注册按钮</t>
+      <t>点击登录按钮</t>
     </r>
     <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
-    <t>测试非法数据是否登录成功（账号）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试非法数据是否登录成功（密码）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>用户数据未注册</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <t>提示用户名或密码错误</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试用户在线状态下是否可以导入某一路径下的全部资料</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户可以正常登录，且可以正常输入相应任务</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <r>
       <t>1.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>输入邮箱</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>:"xiaoming@163.com"</t>
     </r>
     <r>
       <rPr>
@@ -2651,7 +2624,7 @@
         <family val="1"/>
         <charset val="134"/>
       </rPr>
-      <t>，输入密码654321</t>
+      <t>进入日程设置界面</t>
     </r>
     <r>
       <rPr>
@@ -2660,43 +2633,7 @@
         <family val="1"/>
       </rPr>
       <t xml:space="preserve">
-2.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>点击登录按钮</t>
-    </r>
-    <phoneticPr fontId="29" type="noConversion"/>
-  </si>
-  <si>
-    <t>提示密码错误</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>输入邮箱</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>:"xiaoming1@163.com"</t>
+</t>
     </r>
     <r>
       <rPr>
@@ -2705,7 +2642,7 @@
         <family val="1"/>
         <charset val="134"/>
       </rPr>
-      <t>，输入密码123456</t>
+      <t>2</t>
     </r>
     <r>
       <rPr>
@@ -2713,39 +2650,7 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t xml:space="preserve">
-2.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>点击登录按钮</t>
-    </r>
-    <phoneticPr fontId="29" type="noConversion"/>
-  </si>
-  <si>
-    <t>提示用户名或密码错误</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>中</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试用户在线状态下是否可以导入某一路径下的全部资料</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>用户可以正常登录，且可以正常输入相应任务</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1.</t>
+      <t>.</t>
     </r>
     <r>
       <rPr>
@@ -2754,7 +2659,8 @@
         <family val="1"/>
         <charset val="134"/>
       </rPr>
-      <t>进入日程设置界面</t>
+      <t>在输入日程处导入相应的文件
+3.查看是否跳转到</t>
     </r>
     <r>
       <rPr>
@@ -2762,8 +2668,7 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t xml:space="preserve">
-</t>
+      <t>AI</t>
     </r>
     <r>
       <rPr>
@@ -2772,15 +2677,14 @@
         <family val="1"/>
         <charset val="134"/>
       </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>.</t>
+      <t>助手界面
+4.查看AI是否给出相应的规划</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1.</t>
     </r>
     <r>
       <rPr>
@@ -2789,8 +2693,7 @@
         <family val="1"/>
         <charset val="134"/>
       </rPr>
-      <t>在输入日程处导入相应的文件
-3.查看是否跳转到</t>
+      <t>进入日程设置界面</t>
     </r>
     <r>
       <rPr>
@@ -2798,7 +2701,8 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>AI</t>
+      <t xml:space="preserve">
+</t>
     </r>
     <r>
       <rPr>
@@ -2807,14 +2711,15 @@
         <family val="1"/>
         <charset val="134"/>
       </rPr>
-      <t>助手界面
-4.查看AI是否给出相应的规划</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1.</t>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>.</t>
     </r>
     <r>
       <rPr>
@@ -2823,7 +2728,8 @@
         <family val="1"/>
         <charset val="134"/>
       </rPr>
-      <t>进入日程设置界面</t>
+      <t>输入当天日程并明确时间
+3.查看是否跳转到</t>
     </r>
     <r>
       <rPr>
@@ -2831,8 +2737,7 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t xml:space="preserve">
-</t>
+      <t>AI</t>
     </r>
     <r>
       <rPr>
@@ -2841,15 +2746,14 @@
         <family val="1"/>
         <charset val="134"/>
       </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>.</t>
+      <t>助手界面
+4.选择细分任务功能查看</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1.</t>
     </r>
     <r>
       <rPr>
@@ -2858,8 +2762,7 @@
         <family val="1"/>
         <charset val="134"/>
       </rPr>
-      <t>输入当天日程并明确时间
-3.查看是否跳转到</t>
+      <t>进入日程设置界面</t>
     </r>
     <r>
       <rPr>
@@ -2867,7 +2770,8 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>AI</t>
+      <t xml:space="preserve">
+</t>
     </r>
     <r>
       <rPr>
@@ -2876,14 +2780,15 @@
         <family val="1"/>
         <charset val="134"/>
       </rPr>
-      <t>助手界面
-4.选择细分任务功能查看</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1.</t>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>.</t>
     </r>
     <r>
       <rPr>
@@ -2892,7 +2797,8 @@
         <family val="1"/>
         <charset val="134"/>
       </rPr>
-      <t>进入日程设置界面</t>
+      <t>输入当天日程并明确时间
+3.查看是否跳转到</t>
     </r>
     <r>
       <rPr>
@@ -2900,8 +2806,7 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t xml:space="preserve">
-</t>
+      <t>AI</t>
     </r>
     <r>
       <rPr>
@@ -2910,15 +2815,14 @@
         <family val="1"/>
         <charset val="134"/>
       </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>.</t>
+      <t>助手界面
+4.选择提醒事项功能查看</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1.</t>
     </r>
     <r>
       <rPr>
@@ -2927,8 +2831,7 @@
         <family val="1"/>
         <charset val="134"/>
       </rPr>
-      <t>输入当天日程并明确时间
-3.查看是否跳转到</t>
+      <t>进入日程设置界面</t>
     </r>
     <r>
       <rPr>
@@ -2936,7 +2839,8 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>AI</t>
+      <t xml:space="preserve">
+</t>
     </r>
     <r>
       <rPr>
@@ -2945,14 +2849,15 @@
         <family val="1"/>
         <charset val="134"/>
       </rPr>
-      <t>助手界面
-4.选择提醒事项功能查看</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1.</t>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>.</t>
     </r>
     <r>
       <rPr>
@@ -2961,7 +2866,8 @@
         <family val="1"/>
         <charset val="134"/>
       </rPr>
-      <t>进入日程设置界面</t>
+      <t>输入当天日程并不输入明确时间
+3.查看是否跳转到</t>
     </r>
     <r>
       <rPr>
@@ -2969,8 +2875,7 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t xml:space="preserve">
-</t>
+      <t>AI</t>
     </r>
     <r>
       <rPr>
@@ -2979,15 +2884,14 @@
         <family val="1"/>
         <charset val="134"/>
       </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>.</t>
+      <t>助手界面
+4.选择提醒事项功能查看</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1.</t>
     </r>
     <r>
       <rPr>
@@ -2996,8 +2900,7 @@
         <family val="1"/>
         <charset val="134"/>
       </rPr>
-      <t>输入当天日程并不输入明确时间
-3.查看是否跳转到</t>
+      <t>进入日程设置界面</t>
     </r>
     <r>
       <rPr>
@@ -3005,7 +2908,8 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>AI</t>
+      <t xml:space="preserve">
+</t>
     </r>
     <r>
       <rPr>
@@ -3014,14 +2918,15 @@
         <family val="1"/>
         <charset val="134"/>
       </rPr>
-      <t>助手界面
-4.选择提醒事项功能查看</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1.</t>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>.</t>
     </r>
     <r>
       <rPr>
@@ -3030,7 +2935,8 @@
         <family val="1"/>
         <charset val="134"/>
       </rPr>
-      <t>进入日程设置界面</t>
+      <t>输入当天日程并不明确时间
+3.查看是否跳转到</t>
     </r>
     <r>
       <rPr>
@@ -3038,8 +2944,7 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t xml:space="preserve">
-</t>
+      <t>AI</t>
     </r>
     <r>
       <rPr>
@@ -3048,15 +2953,30 @@
         <family val="1"/>
         <charset val="134"/>
       </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>.</t>
+      <t>助手界面
+4.选择细分任务功能查看</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户可以使用AI提醒事项功能，选择删除或保留；AI给出合理的规划，将任务安排到具体时间</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户可以使用AI细分任务功能，选择删除或保留；AI给出合理的规划，将任务安排到具体时间</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试用户输入非法日期是否可以获得阶段总结</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户可以正常登录，且已经输入一段时间的相应日程。假设使用的日期是2024/01/01-2024/01/25</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1.</t>
     </r>
     <r>
       <rPr>
@@ -3065,8 +2985,8 @@
         <family val="1"/>
         <charset val="134"/>
       </rPr>
-      <t>输入当天日程并不明确时间
-3.查看是否跳转到</t>
+      <t xml:space="preserve">进入总结页面
+</t>
     </r>
     <r>
       <rPr>
@@ -3074,7 +2994,7 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>AI</t>
+      <t>2.</t>
     </r>
     <r>
       <rPr>
@@ -3083,25 +3003,24 @@
         <family val="1"/>
         <charset val="134"/>
       </rPr>
-      <t>助手界面
-4.选择细分任务功能查看</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>用户可以使用AI提醒事项功能，选择删除或保留；AI给出合理的规划，将任务安排到具体时间</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>用户可以使用AI细分任务功能，选择删除或保留；AI给出合理的规划，将任务安排到具体时间</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试用户输入非法日期是否可以获得阶段总结</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>用户可以正常登录，且已经输入一段时间的相应日程。假设使用的日期是2024/01/01-2024/01/25</t>
+      <t>选择开始日期和结束日期(2024/02/01,2024/03/23)</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>显示日期错误</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>响应时间符合预期，不调用AI的部分在1.5s内响应，调用AI的部分在5s内响应</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>吞吐量符合预期，可容纳的客户或事务数目标: 不少于10,000</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>可运行时间符合预期，平均每天可以使用22小时以上</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -3115,55 +3034,6 @@
         <family val="1"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">进入总结页面
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>2.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t>选择开始日期和结束日期(2024/02/01,2024/03/23)</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>显示日期错误</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>响应时间符合预期，不调用AI的部分在1.5s内响应，调用AI的部分在5s内响应</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>吞吐量符合预期，可容纳的客户或事务数目标: 不少于10,000</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>可运行时间符合预期，平均每天可以使用22小时以上</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
       <t>在不同分辨率移动端使用软件（1080*2400，720*1280）</t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -3192,9 +3062,6 @@
     <t>TimeGenie-testcase-030</t>
   </si>
   <si>
-    <t>TimeGenie-testcase-031</t>
-  </si>
-  <si>
     <t>2.00</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -3216,16 +3083,12 @@
     <t>N</t>
   </si>
   <si>
-    <t>Low(微小错误)</t>
-  </si>
-  <si>
-    <t>添加邮箱判断</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>转发服务器宕机
 解决方案:切换转发服务器</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Medium(一般错误)</t>
   </si>
 </sst>
 </file>
@@ -3852,63 +3715,6 @@
     <xf numFmtId="0" fontId="17" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3948,6 +3754,63 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -3959,15 +3822,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -3977,17 +3831,26 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4394,80 +4257,80 @@
   <sheetData>
     <row r="1" spans="1:8" ht="51" customHeight="1">
       <c r="A1" s="22"/>
-      <c r="B1" s="69" t="s">
+      <c r="B1" s="50" t="s">
         <v>245</v>
       </c>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
       <c r="G1" s="21"/>
     </row>
     <row r="2" spans="1:8" ht="31.5" customHeight="1">
       <c r="A2" s="16"/>
-      <c r="B2" s="71" t="s">
+      <c r="B2" s="52" t="s">
         <v>216</v>
       </c>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="78" t="s">
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="59" t="s">
         <v>217</v>
       </c>
-      <c r="F2" s="78"/>
+      <c r="F2" s="59"/>
       <c r="G2" s="12"/>
     </row>
     <row r="3" spans="1:8" ht="23.25" customHeight="1">
       <c r="A3" s="16"/>
-      <c r="B3" s="73" t="s">
+      <c r="B3" s="54" t="s">
         <v>255</v>
       </c>
-      <c r="C3" s="74"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="79" t="s">
+      <c r="C3" s="55"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="60" t="s">
         <v>157</v>
       </c>
-      <c r="F3" s="80"/>
+      <c r="F3" s="61"/>
       <c r="G3" s="12"/>
     </row>
     <row r="4" spans="1:8" ht="30">
       <c r="A4" s="16"/>
-      <c r="B4" s="71" t="s">
+      <c r="B4" s="52" t="s">
         <v>213</v>
       </c>
-      <c r="C4" s="76"/>
+      <c r="C4" s="57"/>
       <c r="D4" s="25" t="s">
         <v>214</v>
       </c>
-      <c r="E4" s="79" t="s">
+      <c r="E4" s="60" t="s">
         <v>215</v>
       </c>
-      <c r="F4" s="80"/>
+      <c r="F4" s="61"/>
       <c r="G4" s="12"/>
     </row>
     <row r="5" spans="1:8" ht="27.75" customHeight="1">
       <c r="A5" s="16"/>
-      <c r="B5" s="77">
+      <c r="B5" s="58">
         <v>2</v>
       </c>
-      <c r="C5" s="75"/>
+      <c r="C5" s="56"/>
       <c r="D5" s="37" t="s">
         <v>235</v>
       </c>
-      <c r="E5" s="81" t="s">
+      <c r="E5" s="62" t="s">
         <v>248</v>
       </c>
-      <c r="F5" s="80"/>
+      <c r="F5" s="61"/>
       <c r="G5" s="12"/>
     </row>
     <row r="6" spans="1:8" ht="101.25" customHeight="1">
       <c r="A6" s="20"/>
-      <c r="B6" s="63" t="s">
+      <c r="B6" s="67" t="s">
         <v>256</v>
       </c>
-      <c r="C6" s="64"/>
-      <c r="D6" s="64"/>
-      <c r="E6" s="65"/>
-      <c r="F6" s="66"/>
+      <c r="C6" s="68"/>
+      <c r="D6" s="68"/>
+      <c r="E6" s="69"/>
+      <c r="F6" s="70"/>
       <c r="G6" s="12"/>
     </row>
     <row r="7" spans="1:8" ht="30.5">
@@ -4475,10 +4338,10 @@
       <c r="B7" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="C7" s="67" t="s">
+      <c r="C7" s="72" t="s">
         <v>257</v>
       </c>
-      <c r="D7" s="68"/>
+      <c r="D7" s="73"/>
       <c r="E7" s="3" t="s">
         <v>206</v>
       </c>
@@ -4492,10 +4355,10 @@
       <c r="B8" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="C8" s="67" t="s">
+      <c r="C8" s="72" t="s">
         <v>257</v>
       </c>
-      <c r="D8" s="68"/>
+      <c r="D8" s="73"/>
       <c r="E8" s="3" t="s">
         <v>206</v>
       </c>
@@ -4509,10 +4372,10 @@
       <c r="B9" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="C9" s="67" t="s">
+      <c r="C9" s="72" t="s">
         <v>257</v>
       </c>
-      <c r="D9" s="68"/>
+      <c r="D9" s="73"/>
       <c r="E9" s="3" t="s">
         <v>206</v>
       </c>
@@ -4523,22 +4386,22 @@
     </row>
     <row r="10" spans="1:8" ht="28.5" customHeight="1">
       <c r="A10" s="16"/>
-      <c r="B10" s="56" t="s">
+      <c r="B10" s="77" t="s">
         <v>164</v>
       </c>
-      <c r="C10" s="57"/>
-      <c r="D10" s="57"/>
-      <c r="E10" s="57"/>
-      <c r="F10" s="58"/>
+      <c r="C10" s="78"/>
+      <c r="D10" s="78"/>
+      <c r="E10" s="78"/>
+      <c r="F10" s="79"/>
       <c r="G10" s="12"/>
       <c r="H10" s="12"/>
     </row>
     <row r="11" spans="1:8" ht="32">
       <c r="A11" s="16"/>
-      <c r="B11" s="59" t="s">
+      <c r="B11" s="80" t="s">
         <v>218</v>
       </c>
-      <c r="C11" s="59"/>
+      <c r="C11" s="80"/>
       <c r="D11" s="7" t="s">
         <v>165</v>
       </c>
@@ -4553,10 +4416,10 @@
     </row>
     <row r="12" spans="1:8" ht="15.65" customHeight="1">
       <c r="A12" s="16"/>
-      <c r="B12" s="60">
+      <c r="B12" s="81">
         <v>45480</v>
       </c>
-      <c r="C12" s="60"/>
+      <c r="C12" s="81"/>
       <c r="D12" s="29" t="s">
         <v>166</v>
       </c>
@@ -4571,15 +4434,15 @@
     </row>
     <row r="13" spans="1:8" ht="15.5">
       <c r="A13" s="16"/>
-      <c r="B13" s="60">
+      <c r="B13" s="81">
         <v>45500</v>
       </c>
-      <c r="C13" s="60"/>
+      <c r="C13" s="81"/>
       <c r="D13" s="29" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="E13" s="49" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="F13" s="48" t="s">
         <v>349</v>
@@ -4588,8 +4451,8 @@
     </row>
     <row r="14" spans="1:8" ht="15.5">
       <c r="A14" s="16"/>
-      <c r="B14" s="52"/>
-      <c r="C14" s="53"/>
+      <c r="B14" s="74"/>
+      <c r="C14" s="75"/>
       <c r="D14" s="30"/>
       <c r="E14" s="31"/>
       <c r="F14" s="31"/>
@@ -4597,8 +4460,8 @@
     </row>
     <row r="15" spans="1:8" ht="15.5">
       <c r="A15" s="16"/>
-      <c r="B15" s="52"/>
-      <c r="C15" s="53"/>
+      <c r="B15" s="74"/>
+      <c r="C15" s="75"/>
       <c r="D15" s="30"/>
       <c r="E15" s="31"/>
       <c r="F15" s="31"/>
@@ -4606,8 +4469,8 @@
     </row>
     <row r="16" spans="1:8" ht="15.5">
       <c r="A16" s="16"/>
-      <c r="B16" s="52"/>
-      <c r="C16" s="53"/>
+      <c r="B16" s="74"/>
+      <c r="C16" s="75"/>
       <c r="D16" s="30"/>
       <c r="E16" s="31"/>
       <c r="F16" s="31"/>
@@ -4615,8 +4478,8 @@
     </row>
     <row r="17" spans="1:9" ht="15.5">
       <c r="A17" s="16"/>
-      <c r="B17" s="52"/>
-      <c r="C17" s="53"/>
+      <c r="B17" s="74"/>
+      <c r="C17" s="75"/>
       <c r="D17" s="30"/>
       <c r="E17" s="31"/>
       <c r="F17" s="31"/>
@@ -4624,21 +4487,21 @@
     </row>
     <row r="18" spans="1:9" ht="28.5" customHeight="1">
       <c r="A18" s="22"/>
-      <c r="B18" s="55" t="s">
+      <c r="B18" s="76" t="s">
         <v>234</v>
       </c>
-      <c r="C18" s="55"/>
-      <c r="D18" s="55"/>
-      <c r="E18" s="55"/>
-      <c r="F18" s="55"/>
+      <c r="C18" s="76"/>
+      <c r="D18" s="76"/>
+      <c r="E18" s="76"/>
+      <c r="F18" s="76"/>
       <c r="G18" s="12"/>
     </row>
     <row r="19" spans="1:9" s="11" customFormat="1" ht="17.25" customHeight="1">
       <c r="A19" s="19"/>
-      <c r="B19" s="50" t="s">
+      <c r="B19" s="63" t="s">
         <v>209</v>
       </c>
-      <c r="C19" s="54"/>
+      <c r="C19" s="71"/>
       <c r="D19" s="26" t="s">
         <v>211</v>
       </c>
@@ -4654,20 +4517,20 @@
     </row>
     <row r="20" spans="1:9" s="11" customFormat="1" ht="17.25" customHeight="1">
       <c r="A20" s="19"/>
-      <c r="B20" s="61" t="s">
+      <c r="B20" s="65" t="s">
         <v>229</v>
       </c>
-      <c r="C20" s="62"/>
+      <c r="C20" s="66"/>
       <c r="D20" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E20" s="9">
         <f>SUMPRODUCT(('Test Cases'!C:C=B20)*('Test Cases'!K:K="Y"))</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F20" s="28">
         <f t="shared" ref="F20:F29" si="0">IF(D20,E20/D20,0)</f>
-        <v>0.94444444444444442</v>
+        <v>0.94117647058823528</v>
       </c>
       <c r="G20" s="23"/>
       <c r="H20" s="10"/>
@@ -4675,10 +4538,10 @@
     </row>
     <row r="21" spans="1:9" s="11" customFormat="1" ht="17.25" customHeight="1">
       <c r="A21" s="19"/>
-      <c r="B21" s="50" t="s">
+      <c r="B21" s="63" t="s">
         <v>240</v>
       </c>
-      <c r="C21" s="51"/>
+      <c r="C21" s="64"/>
       <c r="D21" s="9">
         <v>2</v>
       </c>
@@ -4696,10 +4559,10 @@
     </row>
     <row r="22" spans="1:9" s="11" customFormat="1" ht="17.25" customHeight="1">
       <c r="A22" s="19"/>
-      <c r="B22" s="50" t="s">
+      <c r="B22" s="63" t="s">
         <v>241</v>
       </c>
-      <c r="C22" s="51"/>
+      <c r="C22" s="64"/>
       <c r="D22" s="9">
         <v>2</v>
       </c>
@@ -4717,10 +4580,10 @@
     </row>
     <row r="23" spans="1:9" s="11" customFormat="1" ht="17.25" customHeight="1">
       <c r="A23" s="19"/>
-      <c r="B23" s="50" t="s">
+      <c r="B23" s="63" t="s">
         <v>242</v>
       </c>
-      <c r="C23" s="51"/>
+      <c r="C23" s="64"/>
       <c r="D23" s="9">
         <v>1</v>
       </c>
@@ -4738,10 +4601,10 @@
     </row>
     <row r="24" spans="1:9" s="11" customFormat="1" ht="17.25" customHeight="1">
       <c r="A24" s="19"/>
-      <c r="B24" s="50" t="s">
+      <c r="B24" s="63" t="s">
         <v>243</v>
       </c>
-      <c r="C24" s="51"/>
+      <c r="C24" s="64"/>
       <c r="D24" s="9">
         <v>2</v>
       </c>
@@ -4759,10 +4622,10 @@
     </row>
     <row r="25" spans="1:9" s="11" customFormat="1" ht="17.25" customHeight="1">
       <c r="A25" s="19"/>
-      <c r="B25" s="50" t="s">
+      <c r="B25" s="63" t="s">
         <v>244</v>
       </c>
-      <c r="C25" s="51"/>
+      <c r="C25" s="64"/>
       <c r="D25" s="9">
         <v>1</v>
       </c>
@@ -4780,10 +4643,10 @@
     </row>
     <row r="26" spans="1:9" s="11" customFormat="1" ht="17.25" customHeight="1">
       <c r="A26" s="19"/>
-      <c r="B26" s="50" t="s">
+      <c r="B26" s="63" t="s">
         <v>230</v>
       </c>
-      <c r="C26" s="54"/>
+      <c r="C26" s="71"/>
       <c r="D26" s="9">
         <v>1</v>
       </c>
@@ -4801,10 +4664,10 @@
     </row>
     <row r="27" spans="1:9" s="11" customFormat="1" ht="17.25" customHeight="1">
       <c r="A27" s="19"/>
-      <c r="B27" s="50" t="s">
+      <c r="B27" s="63" t="s">
         <v>231</v>
       </c>
-      <c r="C27" s="54"/>
+      <c r="C27" s="71"/>
       <c r="D27" s="9">
         <v>2</v>
       </c>
@@ -4820,10 +4683,10 @@
     </row>
     <row r="28" spans="1:9" s="11" customFormat="1" ht="17.25" customHeight="1">
       <c r="A28" s="19"/>
-      <c r="B28" s="50" t="s">
+      <c r="B28" s="63" t="s">
         <v>232</v>
       </c>
-      <c r="C28" s="54"/>
+      <c r="C28" s="71"/>
       <c r="D28" s="9">
         <v>2</v>
       </c>
@@ -4839,21 +4702,21 @@
     </row>
     <row r="29" spans="1:9" ht="16">
       <c r="A29" s="24"/>
-      <c r="B29" s="50" t="s">
+      <c r="B29" s="63" t="s">
         <v>233</v>
       </c>
-      <c r="C29" s="54"/>
+      <c r="C29" s="71"/>
       <c r="D29" s="9">
         <f>D20+D21+D22+D23+D24+D25+D26+D27+D28</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E29" s="9">
         <f>COUNTIF('Test Cases'!K:K,"Y")</f>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F29" s="28">
         <f t="shared" si="0"/>
-        <v>0.967741935483871</v>
+        <v>0.96666666666666667</v>
       </c>
       <c r="G29" s="12"/>
     </row>
@@ -4918,23 +4781,6 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="C9:D9"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B29:C29"/>
@@ -4951,6 +4797,23 @@
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="E5:F5"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
@@ -4966,7 +4829,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AP893"/>
+  <dimension ref="A1:AP892"/>
   <sheetFormatPr defaultColWidth="13.08203125" defaultRowHeight="15.5"/>
   <cols>
     <col min="1" max="1" width="13.75" style="34" customWidth="1"/>
@@ -5108,10 +4971,10 @@
       </c>
       <c r="J5" s="43"/>
       <c r="K5" s="6" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="M5" s="32" t="s">
         <v>160</v>
@@ -5129,72 +4992,70 @@
         <v>228</v>
       </c>
       <c r="D6" s="46" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E6" s="45" t="s">
         <v>237</v>
       </c>
       <c r="F6" s="46" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="G6" s="6"/>
       <c r="H6" s="6" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="I6" s="46" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="J6" s="43"/>
       <c r="K6" s="6" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="M6" s="32" t="s">
         <v>161</v>
       </c>
       <c r="N6" s="6"/>
     </row>
-    <row r="7" spans="1:42" ht="101.5">
+    <row r="7" spans="1:42" ht="73">
       <c r="A7" s="6" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="B7" s="46" t="s">
-        <v>383</v>
+        <v>261</v>
       </c>
       <c r="C7" s="44" t="s">
         <v>382</v>
       </c>
       <c r="D7" s="46" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E7" s="45" t="s">
         <v>237</v>
       </c>
       <c r="F7" s="46" t="s">
-        <v>426</v>
+        <v>388</v>
       </c>
       <c r="G7" s="6"/>
       <c r="H7" s="6" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="I7" s="46" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="J7" s="43"/>
       <c r="K7" s="6" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="M7" s="32"/>
-      <c r="N7" s="44" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="8" spans="1:42" ht="73">
+      <c r="N7" s="6"/>
+    </row>
+    <row r="8" spans="1:42" ht="58.5">
       <c r="A8" s="6" t="s">
         <v>350</v>
       </c>
@@ -5205,27 +5066,27 @@
         <v>382</v>
       </c>
       <c r="D8" s="46" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="E8" s="45" t="s">
         <v>237</v>
       </c>
       <c r="F8" s="46" t="s">
-        <v>392</v>
+        <v>264</v>
       </c>
       <c r="G8" s="6"/>
       <c r="H8" s="6" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="I8" s="46" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="J8" s="43"/>
       <c r="K8" s="6" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="M8" s="32"/>
       <c r="N8" s="6"/>
@@ -5238,150 +5099,154 @@
         <v>261</v>
       </c>
       <c r="C9" s="44" t="s">
-        <v>382</v>
-      </c>
-      <c r="D9" s="46" t="s">
-        <v>391</v>
+        <v>262</v>
+      </c>
+      <c r="D9" s="47" t="s">
+        <v>263</v>
       </c>
       <c r="E9" s="45" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="F9" s="46" t="s">
         <v>264</v>
       </c>
       <c r="G9" s="6"/>
       <c r="H9" s="6" t="s">
-        <v>393</v>
+        <v>317</v>
       </c>
       <c r="I9" s="46" t="s">
-        <v>394</v>
+        <v>325</v>
       </c>
       <c r="J9" s="43"/>
       <c r="K9" s="6" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>427</v>
-      </c>
-      <c r="M9" s="32"/>
+        <v>422</v>
+      </c>
+      <c r="M9" s="32" t="s">
+        <v>162</v>
+      </c>
       <c r="N9" s="6"/>
-    </row>
-    <row r="10" spans="1:42" ht="58.5">
+      <c r="X9" s="33"/>
+    </row>
+    <row r="10" spans="1:42" ht="86">
       <c r="A10" s="6" t="s">
         <v>352</v>
       </c>
       <c r="B10" s="46" t="s">
-        <v>261</v>
-      </c>
-      <c r="C10" s="44" t="s">
-        <v>262</v>
-      </c>
-      <c r="D10" s="47" t="s">
-        <v>263</v>
+        <v>265</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="D10" s="44" t="s">
+        <v>267</v>
       </c>
       <c r="E10" s="45" t="s">
         <v>251</v>
       </c>
-      <c r="F10" s="46" t="s">
-        <v>264</v>
+      <c r="F10" s="43" t="s">
+        <v>254</v>
       </c>
       <c r="G10" s="6"/>
       <c r="H10" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="I10" s="46" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="J10" s="43"/>
       <c r="K10" s="6" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="M10" s="32" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="N10" s="6"/>
       <c r="X10" s="33"/>
     </row>
-    <row r="11" spans="1:42" ht="86">
+    <row r="11" spans="1:42" ht="43">
       <c r="A11" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="B11" s="46" t="s">
-        <v>265</v>
+      <c r="B11" s="44" t="s">
+        <v>266</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>228</v>
       </c>
       <c r="D11" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="E11" s="45" t="s">
-        <v>251</v>
-      </c>
-      <c r="F11" s="43" t="s">
-        <v>254</v>
+        <v>268</v>
+      </c>
+      <c r="E11" s="36" t="s">
+        <v>279</v>
+      </c>
+      <c r="F11" s="44" t="s">
+        <v>309</v>
       </c>
       <c r="G11" s="6"/>
-      <c r="H11" s="6" t="s">
-        <v>318</v>
-      </c>
-      <c r="I11" s="46" t="s">
-        <v>326</v>
-      </c>
-      <c r="J11" s="43"/>
+      <c r="H11" s="44" t="s">
+        <v>319</v>
+      </c>
+      <c r="I11" s="44" t="s">
+        <v>327</v>
+      </c>
+      <c r="J11" s="6"/>
       <c r="K11" s="6" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>427</v>
-      </c>
-      <c r="M11" s="32" t="s">
-        <v>163</v>
-      </c>
+        <v>422</v>
+      </c>
+      <c r="M11" s="32"/>
       <c r="N11" s="6"/>
       <c r="X11" s="33"/>
+      <c r="AP11" s="5" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="12" spans="1:42" ht="43">
       <c r="A12" s="6" t="s">
         <v>354</v>
       </c>
       <c r="B12" s="44" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>228</v>
       </c>
       <c r="D12" s="44" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E12" s="36" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F12" s="44" t="s">
-        <v>309</v>
-      </c>
-      <c r="G12" s="6"/>
-      <c r="H12" s="44" t="s">
-        <v>319</v>
+        <v>311</v>
+      </c>
+      <c r="G12" s="44"/>
+      <c r="H12" s="6" t="s">
+        <v>320</v>
       </c>
       <c r="I12" s="44" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="J12" s="6"/>
       <c r="K12" s="6" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="M12" s="32"/>
       <c r="N12" s="6"/>
       <c r="X12" s="33"/>
       <c r="AP12" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13" spans="1:42" ht="43">
@@ -5395,15 +5260,15 @@
         <v>228</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E13" s="36" t="s">
         <v>280</v>
       </c>
       <c r="F13" s="44" t="s">
-        <v>311</v>
-      </c>
-      <c r="G13" s="44"/>
+        <v>310</v>
+      </c>
+      <c r="G13" s="42"/>
       <c r="H13" s="6" t="s">
         <v>320</v>
       </c>
@@ -5412,19 +5277,20 @@
       </c>
       <c r="J13" s="6"/>
       <c r="K13" s="6" t="s">
+        <v>423</v>
+      </c>
+      <c r="L13" s="6" t="s">
         <v>425</v>
       </c>
-      <c r="L13" s="6" t="s">
-        <v>427</v>
-      </c>
       <c r="M13" s="32"/>
-      <c r="N13" s="6"/>
-      <c r="X13" s="33"/>
+      <c r="N13" s="44" t="s">
+        <v>424</v>
+      </c>
       <c r="AP13" s="5" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="14" spans="1:42" ht="43">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="14" spans="1:42" ht="44">
       <c r="A14" s="6" t="s">
         <v>356</v>
       </c>
@@ -5435,74 +5301,69 @@
         <v>228</v>
       </c>
       <c r="D14" s="44" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E14" s="36" t="s">
         <v>280</v>
       </c>
       <c r="F14" s="44" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G14" s="42"/>
       <c r="H14" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="I14" s="44" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="J14" s="6"/>
       <c r="K14" s="6" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="M14" s="32"/>
-      <c r="N14" s="44" t="s">
-        <v>431</v>
-      </c>
+      <c r="N14" s="6"/>
       <c r="AP14" s="5" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="15" spans="1:42" ht="44">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="15" spans="1:42" ht="100.5">
       <c r="A15" s="6" t="s">
         <v>357</v>
       </c>
       <c r="B15" s="44" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>228</v>
       </c>
       <c r="D15" s="44" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E15" s="36" t="s">
         <v>280</v>
       </c>
       <c r="F15" s="44" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="G15" s="42"/>
       <c r="H15" s="6" t="s">
-        <v>321</v>
+        <v>398</v>
       </c>
       <c r="I15" s="44" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="J15" s="6"/>
       <c r="K15" s="6" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="M15" s="32"/>
       <c r="N15" s="6"/>
-      <c r="AP15" s="5" t="s">
-        <v>163</v>
-      </c>
     </row>
     <row r="16" spans="1:42" ht="100.5">
       <c r="A16" s="6" t="s">
@@ -5525,17 +5386,17 @@
       </c>
       <c r="G16" s="42"/>
       <c r="H16" s="6" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="I16" s="44" t="s">
-        <v>331</v>
+        <v>401</v>
       </c>
       <c r="J16" s="6"/>
       <c r="K16" s="6" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="M16" s="32"/>
       <c r="N16" s="6"/>
@@ -5551,7 +5412,7 @@
         <v>228</v>
       </c>
       <c r="D17" s="44" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E17" s="36" t="s">
         <v>280</v>
@@ -5561,17 +5422,17 @@
       </c>
       <c r="G17" s="42"/>
       <c r="H17" s="6" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="I17" s="44" t="s">
-        <v>405</v>
+        <v>330</v>
       </c>
       <c r="J17" s="6"/>
       <c r="K17" s="6" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="M17" s="32"/>
       <c r="N17" s="6"/>
@@ -5597,17 +5458,17 @@
       </c>
       <c r="G18" s="42"/>
       <c r="H18" s="6" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="I18" s="44" t="s">
-        <v>330</v>
+        <v>402</v>
       </c>
       <c r="J18" s="6"/>
       <c r="K18" s="6" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="M18" s="32"/>
       <c r="N18" s="6"/>
@@ -5623,32 +5484,32 @@
         <v>228</v>
       </c>
       <c r="D19" s="44" t="s">
-        <v>273</v>
+        <v>394</v>
       </c>
       <c r="E19" s="36" t="s">
-        <v>280</v>
+        <v>393</v>
       </c>
       <c r="F19" s="44" t="s">
-        <v>312</v>
+        <v>395</v>
       </c>
       <c r="G19" s="42"/>
       <c r="H19" s="6" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="I19" s="44" t="s">
-        <v>406</v>
+        <v>330</v>
       </c>
       <c r="J19" s="6"/>
       <c r="K19" s="6" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="M19" s="32"/>
       <c r="N19" s="6"/>
     </row>
-    <row r="20" spans="1:14" ht="100.5">
+    <row r="20" spans="1:14" ht="44">
       <c r="A20" s="6" t="s">
         <v>362</v>
       </c>
@@ -5659,32 +5520,32 @@
         <v>228</v>
       </c>
       <c r="D20" s="44" t="s">
-        <v>398</v>
+        <v>274</v>
       </c>
       <c r="E20" s="36" t="s">
-        <v>397</v>
+        <v>281</v>
       </c>
       <c r="F20" s="44" t="s">
-        <v>399</v>
-      </c>
-      <c r="G20" s="42"/>
+        <v>313</v>
+      </c>
+      <c r="G20" s="43"/>
       <c r="H20" s="6" t="s">
-        <v>400</v>
+        <v>322</v>
       </c>
       <c r="I20" s="44" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="J20" s="6"/>
       <c r="K20" s="6" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="M20" s="32"/>
       <c r="N20" s="6"/>
     </row>
-    <row r="21" spans="1:14" ht="44">
+    <row r="21" spans="1:14" ht="85">
       <c r="A21" s="6" t="s">
         <v>363</v>
       </c>
@@ -5695,187 +5556,187 @@
         <v>228</v>
       </c>
       <c r="D21" s="44" t="s">
-        <v>274</v>
+        <v>403</v>
       </c>
       <c r="E21" s="36" t="s">
         <v>281</v>
       </c>
       <c r="F21" s="44" t="s">
-        <v>313</v>
+        <v>404</v>
       </c>
       <c r="G21" s="43"/>
       <c r="H21" s="6" t="s">
-        <v>322</v>
+        <v>405</v>
       </c>
       <c r="I21" s="44" t="s">
-        <v>332</v>
+        <v>406</v>
       </c>
       <c r="J21" s="6"/>
       <c r="K21" s="6" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="M21" s="32"/>
       <c r="N21" s="6"/>
     </row>
-    <row r="22" spans="1:14" ht="85">
+    <row r="22" spans="1:14" ht="57.5">
       <c r="A22" s="6" t="s">
         <v>364</v>
       </c>
       <c r="B22" s="44" t="s">
-        <v>276</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>228</v>
+        <v>277</v>
+      </c>
+      <c r="C22" s="44" t="s">
+        <v>282</v>
       </c>
       <c r="D22" s="44" t="s">
-        <v>407</v>
+        <v>278</v>
       </c>
       <c r="E22" s="36" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F22" s="44" t="s">
-        <v>408</v>
+        <v>314</v>
       </c>
       <c r="G22" s="43"/>
       <c r="H22" s="6" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="I22" s="44" t="s">
-        <v>410</v>
+        <v>333</v>
       </c>
       <c r="J22" s="6"/>
       <c r="K22" s="6" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="M22" s="32"/>
       <c r="N22" s="6"/>
     </row>
-    <row r="23" spans="1:14" ht="57.5">
+    <row r="23" spans="1:14" ht="115">
       <c r="A23" s="6" t="s">
         <v>365</v>
       </c>
       <c r="B23" s="44" t="s">
-        <v>277</v>
-      </c>
-      <c r="C23" s="44" t="s">
-        <v>282</v>
+        <v>283</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>284</v>
       </c>
       <c r="D23" s="44" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="E23" s="36" t="s">
         <v>280</v>
       </c>
       <c r="F23" s="44" t="s">
-        <v>314</v>
-      </c>
-      <c r="G23" s="43"/>
+        <v>315</v>
+      </c>
+      <c r="G23" s="6"/>
       <c r="H23" s="6" t="s">
-        <v>414</v>
+        <v>323</v>
       </c>
       <c r="I23" s="44" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="J23" s="6"/>
       <c r="K23" s="6" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="L23" s="6" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="M23" s="32"/>
       <c r="N23" s="6"/>
     </row>
-    <row r="24" spans="1:14" ht="115">
+    <row r="24" spans="1:14" ht="71">
       <c r="A24" s="6" t="s">
         <v>366</v>
       </c>
       <c r="B24" s="44" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>284</v>
       </c>
       <c r="D24" s="44" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E24" s="36" t="s">
         <v>280</v>
       </c>
       <c r="F24" s="44" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="G24" s="6"/>
-      <c r="H24" s="6" t="s">
-        <v>323</v>
+      <c r="H24" s="44" t="s">
+        <v>336</v>
       </c>
       <c r="I24" s="44" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="J24" s="6"/>
       <c r="K24" s="6" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="M24" s="32"/>
       <c r="N24" s="6"/>
     </row>
-    <row r="25" spans="1:14" ht="71">
+    <row r="25" spans="1:14" ht="141">
       <c r="A25" s="6" t="s">
         <v>367</v>
       </c>
       <c r="B25" s="44" t="s">
-        <v>285</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>284</v>
+        <v>289</v>
+      </c>
+      <c r="C25" s="44" t="s">
+        <v>288</v>
       </c>
       <c r="D25" s="44" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="E25" s="36" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F25" s="44" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G25" s="6"/>
       <c r="H25" s="44" t="s">
-        <v>336</v>
+        <v>411</v>
       </c>
       <c r="I25" s="44" t="s">
-        <v>335</v>
+        <v>407</v>
       </c>
       <c r="J25" s="6"/>
       <c r="K25" s="6" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="L25" s="6" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="M25" s="32"/>
       <c r="N25" s="6"/>
     </row>
-    <row r="26" spans="1:14" ht="141">
+    <row r="26" spans="1:14" ht="113">
       <c r="A26" s="6" t="s">
         <v>368</v>
       </c>
       <c r="B26" s="44" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C26" s="44" t="s">
         <v>288</v>
       </c>
       <c r="D26" s="44" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="E26" s="36" t="s">
         <v>281</v>
@@ -5885,33 +5746,33 @@
       </c>
       <c r="G26" s="6"/>
       <c r="H26" s="44" t="s">
-        <v>415</v>
+        <v>337</v>
       </c>
       <c r="I26" s="44" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="J26" s="6"/>
       <c r="K26" s="6" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="M26" s="32"/>
       <c r="N26" s="6"/>
     </row>
-    <row r="27" spans="1:14" ht="113">
+    <row r="27" spans="1:14" ht="127">
       <c r="A27" s="6" t="s">
         <v>369</v>
       </c>
       <c r="B27" s="44" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C27" s="44" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="D27" s="44" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E27" s="36" t="s">
         <v>281</v>
@@ -5921,33 +5782,33 @@
       </c>
       <c r="G27" s="6"/>
       <c r="H27" s="44" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="I27" s="44" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="J27" s="6"/>
       <c r="K27" s="6" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="L27" s="6" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="M27" s="32"/>
       <c r="N27" s="6"/>
     </row>
-    <row r="28" spans="1:14" ht="127">
+    <row r="28" spans="1:14" ht="71">
       <c r="A28" s="6" t="s">
         <v>371</v>
       </c>
       <c r="B28" s="44" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="C28" s="44" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="D28" s="44" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="E28" s="36" t="s">
         <v>281</v>
@@ -5957,17 +5818,17 @@
       </c>
       <c r="G28" s="6"/>
       <c r="H28" s="44" t="s">
-        <v>342</v>
+        <v>324</v>
       </c>
       <c r="I28" s="44" t="s">
-        <v>413</v>
+        <v>343</v>
       </c>
       <c r="J28" s="6"/>
       <c r="K28" s="6" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="M28" s="32"/>
       <c r="N28" s="6"/>
@@ -5977,13 +5838,13 @@
         <v>372</v>
       </c>
       <c r="B29" s="44" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="C29" s="44" t="s">
-        <v>296</v>
-      </c>
-      <c r="D29" s="44" t="s">
-        <v>298</v>
+        <v>299</v>
+      </c>
+      <c r="D29" s="46" t="s">
+        <v>300</v>
       </c>
       <c r="E29" s="36" t="s">
         <v>281</v>
@@ -5993,33 +5854,33 @@
       </c>
       <c r="G29" s="6"/>
       <c r="H29" s="44" t="s">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="I29" s="44" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="J29" s="6"/>
       <c r="K29" s="6" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="L29" s="6" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="M29" s="32"/>
       <c r="N29" s="6"/>
     </row>
     <row r="30" spans="1:14" ht="71">
       <c r="A30" s="6" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="B30" s="44" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C30" s="44" t="s">
         <v>299</v>
       </c>
       <c r="D30" s="46" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E30" s="36" t="s">
         <v>281</v>
@@ -6029,69 +5890,69 @@
       </c>
       <c r="G30" s="6"/>
       <c r="H30" s="44" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="I30" s="44" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="J30" s="6"/>
       <c r="K30" s="6" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="M30" s="32"/>
       <c r="N30" s="6"/>
     </row>
-    <row r="31" spans="1:14" ht="71">
+    <row r="31" spans="1:14" ht="57">
       <c r="A31" s="6" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="B31" s="44" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C31" s="44" t="s">
-        <v>299</v>
-      </c>
-      <c r="D31" s="46" t="s">
-        <v>301</v>
+        <v>304</v>
+      </c>
+      <c r="D31" s="44" t="s">
+        <v>306</v>
       </c>
       <c r="E31" s="36" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F31" s="44" t="s">
         <v>315</v>
       </c>
       <c r="G31" s="6"/>
       <c r="H31" s="44" t="s">
-        <v>340</v>
-      </c>
-      <c r="I31" s="44" t="s">
-        <v>345</v>
+        <v>338</v>
+      </c>
+      <c r="I31" s="46" t="s">
+        <v>346</v>
       </c>
       <c r="J31" s="6"/>
       <c r="K31" s="6" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="L31" s="6" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="M31" s="32"/>
       <c r="N31" s="6"/>
     </row>
-    <row r="32" spans="1:14" ht="57">
+    <row r="32" spans="1:14" ht="85">
       <c r="A32" s="6" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="B32" s="44" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C32" s="44" t="s">
         <v>304</v>
       </c>
       <c r="D32" s="44" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E32" s="36" t="s">
         <v>280</v>
@@ -6101,69 +5962,69 @@
       </c>
       <c r="G32" s="6"/>
       <c r="H32" s="44" t="s">
-        <v>338</v>
-      </c>
-      <c r="I32" s="46" t="s">
-        <v>346</v>
+        <v>339</v>
+      </c>
+      <c r="I32" s="44" t="s">
+        <v>347</v>
       </c>
       <c r="J32" s="6"/>
       <c r="K32" s="6" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="M32" s="32"/>
       <c r="N32" s="6"/>
     </row>
-    <row r="33" spans="1:14" ht="85">
+    <row r="33" spans="1:14" ht="99">
       <c r="A33" s="6" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="B33" s="44" t="s">
-        <v>308</v>
-      </c>
-      <c r="C33" s="44" t="s">
-        <v>304</v>
+        <v>374</v>
+      </c>
+      <c r="C33" s="46" t="s">
+        <v>370</v>
       </c>
       <c r="D33" s="44" t="s">
-        <v>307</v>
+        <v>375</v>
       </c>
       <c r="E33" s="36" t="s">
-        <v>280</v>
+        <v>237</v>
       </c>
       <c r="F33" s="44" t="s">
-        <v>315</v>
+        <v>377</v>
       </c>
       <c r="G33" s="6"/>
-      <c r="H33" s="44" t="s">
-        <v>339</v>
+      <c r="H33" s="46" t="s">
+        <v>381</v>
       </c>
       <c r="I33" s="44" t="s">
-        <v>347</v>
+        <v>380</v>
       </c>
       <c r="J33" s="6"/>
       <c r="K33" s="6" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="L33" s="6" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="M33" s="32"/>
       <c r="N33" s="6"/>
     </row>
-    <row r="34" spans="1:14" ht="99">
+    <row r="34" spans="1:14" ht="72">
       <c r="A34" s="6" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="B34" s="44" t="s">
-        <v>374</v>
-      </c>
-      <c r="C34" s="46" t="s">
+        <v>373</v>
+      </c>
+      <c r="C34" s="6" t="s">
         <v>370</v>
       </c>
       <c r="D34" s="44" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E34" s="36" t="s">
         <v>237</v>
@@ -6172,55 +6033,35 @@
         <v>377</v>
       </c>
       <c r="G34" s="6"/>
-      <c r="H34" s="46" t="s">
-        <v>381</v>
+      <c r="H34" s="6" t="s">
+        <v>378</v>
       </c>
       <c r="I34" s="44" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="J34" s="6"/>
       <c r="K34" s="6" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="M34" s="32"/>
       <c r="N34" s="6"/>
     </row>
-    <row r="35" spans="1:14" ht="72">
-      <c r="A35" s="6" t="s">
-        <v>422</v>
-      </c>
-      <c r="B35" s="44" t="s">
-        <v>373</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>370</v>
-      </c>
-      <c r="D35" s="44" t="s">
-        <v>376</v>
-      </c>
-      <c r="E35" s="36" t="s">
-        <v>237</v>
-      </c>
-      <c r="F35" s="44" t="s">
-        <v>377</v>
-      </c>
+    <row r="35" spans="1:14">
+      <c r="A35" s="6"/>
+      <c r="B35" s="44"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="44"/>
+      <c r="E35" s="36"/>
+      <c r="F35" s="44"/>
       <c r="G35" s="6"/>
-      <c r="H35" s="6" t="s">
-        <v>378</v>
-      </c>
-      <c r="I35" s="44" t="s">
-        <v>379</v>
-      </c>
+      <c r="H35" s="42"/>
+      <c r="I35" s="42"/>
       <c r="J35" s="6"/>
-      <c r="K35" s="6" t="s">
-        <v>425</v>
-      </c>
-      <c r="L35" s="6" t="s">
-        <v>427</v>
-      </c>
+      <c r="K35" s="6"/>
+      <c r="L35" s="6"/>
       <c r="M35" s="32"/>
       <c r="N35" s="6"/>
     </row>
@@ -6228,12 +6069,12 @@
       <c r="A36" s="6"/>
       <c r="B36" s="44"/>
       <c r="C36" s="6"/>
-      <c r="D36" s="44"/>
+      <c r="D36" s="42"/>
       <c r="E36" s="36"/>
       <c r="F36" s="44"/>
       <c r="G36" s="6"/>
-      <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
+      <c r="H36" s="6"/>
+      <c r="I36" s="44"/>
       <c r="J36" s="6"/>
       <c r="K36" s="6"/>
       <c r="L36" s="6"/>
@@ -6258,14 +6099,14 @@
     </row>
     <row r="38" spans="1:14">
       <c r="A38" s="6"/>
-      <c r="B38" s="44"/>
+      <c r="B38" s="6"/>
       <c r="C38" s="6"/>
-      <c r="D38" s="42"/>
+      <c r="D38" s="6"/>
       <c r="E38" s="36"/>
-      <c r="F38" s="44"/>
+      <c r="F38" s="6"/>
       <c r="G38" s="6"/>
       <c r="H38" s="6"/>
-      <c r="I38" s="44"/>
+      <c r="I38" s="6"/>
       <c r="J38" s="6"/>
       <c r="K38" s="6"/>
       <c r="L38" s="6"/>
@@ -6450,14 +6291,8 @@
     </row>
     <row r="50" spans="1:14">
       <c r="A50" s="6"/>
-      <c r="B50" s="6"/>
       <c r="C50" s="6"/>
-      <c r="D50" s="6"/>
       <c r="E50" s="36"/>
-      <c r="F50" s="6"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="6"/>
-      <c r="I50" s="6"/>
       <c r="J50" s="6"/>
       <c r="K50" s="6"/>
       <c r="L50" s="6"/>
@@ -6565,7 +6400,6 @@
       <c r="N60" s="6"/>
     </row>
     <row r="61" spans="1:14">
-      <c r="A61" s="6"/>
       <c r="C61" s="6"/>
       <c r="E61" s="36"/>
       <c r="J61" s="6"/>
@@ -6613,16 +6447,12 @@
     <row r="66" spans="3:14">
       <c r="C66" s="6"/>
       <c r="E66" s="36"/>
-      <c r="J66" s="6"/>
       <c r="K66" s="6"/>
       <c r="L66" s="6"/>
-      <c r="M66" s="32"/>
-      <c r="N66" s="6"/>
     </row>
     <row r="67" spans="3:14">
       <c r="C67" s="6"/>
       <c r="E67" s="36"/>
-      <c r="K67" s="6"/>
       <c r="L67" s="6"/>
     </row>
     <row r="68" spans="3:14">
@@ -10402,7 +10232,6 @@
     </row>
     <row r="823" spans="3:12">
       <c r="C823" s="6"/>
-      <c r="E823" s="36"/>
       <c r="L823" s="6"/>
     </row>
     <row r="824" spans="3:12">
@@ -10651,7 +10480,6 @@
     </row>
     <row r="885" spans="3:12">
       <c r="C885" s="6"/>
-      <c r="L885" s="6"/>
     </row>
     <row r="886" spans="3:12">
       <c r="C886" s="6"/>
@@ -10673,9 +10501,6 @@
     </row>
     <row r="892" spans="3:12">
       <c r="C892" s="6"/>
-    </row>
-    <row r="893" spans="3:12">
-      <c r="C893" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -10686,16 +10511,16 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K4" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>$X$5:$X$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K5:K65541" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K5:K65540" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:C65525" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:C65524" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"功能测试,性能测试,易用性测试,可靠性测试,安全性测试,兼容性测试,界面测试,压力测试,部署测试"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5:E823" xr:uid="{00000000-0002-0000-0100-000003000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5:E822" xr:uid="{00000000-0002-0000-0100-000003000000}">
       <formula1>"高,中,低"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L5:L885" xr:uid="{00000000-0002-0000-0100-000004000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L5:L884" xr:uid="{00000000-0002-0000-0100-000004000000}">
       <formula1>"Null(无缺陷),Urgent(严重错误),High(主要错误),Medium(一般错误),Low(微小错误)"</formula1>
     </dataValidation>
   </dataValidations>
@@ -10722,10 +10547,10 @@
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="87" t="s">
+      <c r="A3" s="94" t="s">
         <v>239</v>
       </c>
-      <c r="B3" s="87"/>
+      <c r="B3" s="94"/>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="38" t="s">
@@ -10762,19 +10587,19 @@
       <c r="B9" s="39"/>
     </row>
     <row r="10" spans="1:2" ht="27" customHeight="1">
-      <c r="A10" s="86" t="s">
+      <c r="A10" s="88" t="s">
         <v>204</v>
       </c>
-      <c r="B10" s="86"/>
+      <c r="B10" s="88"/>
     </row>
     <row r="11" spans="1:2" ht="24.75" customHeight="1">
-      <c r="A11" s="85" t="s">
+      <c r="A11" s="91" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="85"/>
+      <c r="B11" s="91"/>
     </row>
     <row r="12" spans="1:2" ht="24.75" customHeight="1">
-      <c r="A12" s="85" t="s">
+      <c r="A12" s="91" t="s">
         <v>14</v>
       </c>
       <c r="B12" s="2" t="s">
@@ -10782,85 +10607,85 @@
       </c>
     </row>
     <row r="13" spans="1:2" ht="20.25" customHeight="1">
-      <c r="A13" s="85"/>
+      <c r="A13" s="91"/>
       <c r="B13" s="2" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="33.75" customHeight="1">
-      <c r="A14" s="85"/>
+      <c r="A14" s="91"/>
       <c r="B14" s="2" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="18.75" customHeight="1">
-      <c r="A15" s="85"/>
+      <c r="A15" s="91"/>
       <c r="B15" s="2" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="36.75" customHeight="1">
-      <c r="A16" s="85"/>
+      <c r="A16" s="91"/>
       <c r="B16" s="2" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="36.75" customHeight="1">
-      <c r="A17" s="85"/>
+      <c r="A17" s="91"/>
       <c r="B17" s="2" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="37.5" customHeight="1">
-      <c r="A18" s="85"/>
+      <c r="A18" s="91"/>
       <c r="B18" s="2" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="50.25" customHeight="1">
-      <c r="A19" s="85"/>
+      <c r="A19" s="91"/>
       <c r="B19" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="18" customHeight="1">
-      <c r="A20" s="85"/>
+      <c r="A20" s="91"/>
       <c r="B20" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="18" customHeight="1">
-      <c r="A21" s="85"/>
+      <c r="A21" s="91"/>
       <c r="B21" s="2" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="27">
-      <c r="A22" s="85"/>
+      <c r="A22" s="91"/>
       <c r="B22" s="2" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A23" s="85"/>
+      <c r="A23" s="91"/>
       <c r="B23" s="2" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A24" s="85"/>
+      <c r="A24" s="91"/>
       <c r="B24" s="2" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="22.5" customHeight="1">
-      <c r="A25" s="85" t="s">
+      <c r="A25" s="91" t="s">
         <v>32</v>
       </c>
-      <c r="B25" s="85"/>
+      <c r="B25" s="91"/>
     </row>
     <row r="26" spans="1:2" ht="21.75" customHeight="1">
-      <c r="A26" s="85" t="s">
+      <c r="A26" s="91" t="s">
         <v>15</v>
       </c>
       <c r="B26" s="2" t="s">
@@ -10868,61 +10693,61 @@
       </c>
     </row>
     <row r="27" spans="1:2" ht="21.75" customHeight="1">
-      <c r="A27" s="85"/>
+      <c r="A27" s="91"/>
       <c r="B27" s="2" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="21.75" customHeight="1">
-      <c r="A28" s="85"/>
+      <c r="A28" s="91"/>
       <c r="B28" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="21.75" customHeight="1">
-      <c r="A29" s="85"/>
+      <c r="A29" s="91"/>
       <c r="B29" s="2" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="21.75" customHeight="1">
-      <c r="A30" s="85"/>
+      <c r="A30" s="91"/>
       <c r="B30" s="2" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="21.75" customHeight="1">
-      <c r="A31" s="85"/>
+      <c r="A31" s="91"/>
       <c r="B31" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="21.75" customHeight="1">
-      <c r="A32" s="85"/>
+      <c r="A32" s="91"/>
       <c r="B32" s="2" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="21.75" customHeight="1">
-      <c r="A33" s="85"/>
+      <c r="A33" s="91"/>
       <c r="B33" s="2" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="30.75" customHeight="1">
-      <c r="A34" s="85"/>
+      <c r="A34" s="91"/>
       <c r="B34" s="2" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="21.75" customHeight="1">
-      <c r="A35" s="85" t="s">
+      <c r="A35" s="91" t="s">
         <v>42</v>
       </c>
-      <c r="B35" s="85"/>
+      <c r="B35" s="91"/>
     </row>
     <row r="36" spans="1:2" ht="33" customHeight="1">
-      <c r="A36" s="88" t="s">
+      <c r="A36" s="85" t="s">
         <v>31</v>
       </c>
       <c r="B36" s="2" t="s">
@@ -10930,25 +10755,25 @@
       </c>
     </row>
     <row r="37" spans="1:2" ht="45.75" customHeight="1">
-      <c r="A37" s="89"/>
+      <c r="A37" s="86"/>
       <c r="B37" s="2" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="24" customHeight="1">
-      <c r="A38" s="90"/>
+      <c r="A38" s="87"/>
       <c r="B38" s="2" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="27" customHeight="1">
-      <c r="A39" s="85" t="s">
+      <c r="A39" s="91" t="s">
         <v>43</v>
       </c>
-      <c r="B39" s="85"/>
+      <c r="B39" s="91"/>
     </row>
     <row r="40" spans="1:2" ht="22.5" customHeight="1">
-      <c r="A40" s="85" t="s">
+      <c r="A40" s="91" t="s">
         <v>46</v>
       </c>
       <c r="B40" s="2" t="s">
@@ -10956,28 +10781,28 @@
       </c>
     </row>
     <row r="41" spans="1:2" ht="21.75" customHeight="1">
-      <c r="A41" s="85"/>
+      <c r="A41" s="91"/>
       <c r="B41" s="2" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="27">
-      <c r="A42" s="85"/>
+      <c r="A42" s="91"/>
       <c r="B42" s="2" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="25.5" customHeight="1">
-      <c r="A43" s="85"/>
+      <c r="A43" s="91"/>
       <c r="B43" s="2" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="27" customHeight="1">
-      <c r="A44" s="85" t="s">
+      <c r="A44" s="91" t="s">
         <v>50</v>
       </c>
-      <c r="B44" s="85"/>
+      <c r="B44" s="91"/>
     </row>
     <row r="45" spans="1:2" ht="32.25" customHeight="1">
       <c r="A45" s="2" t="s">
@@ -10988,13 +10813,13 @@
       </c>
     </row>
     <row r="46" spans="1:2" ht="27" customHeight="1">
-      <c r="A46" s="85" t="s">
+      <c r="A46" s="91" t="s">
         <v>53</v>
       </c>
-      <c r="B46" s="85"/>
+      <c r="B46" s="91"/>
     </row>
     <row r="47" spans="1:2" ht="27" customHeight="1">
-      <c r="A47" s="85" t="s">
+      <c r="A47" s="91" t="s">
         <v>58</v>
       </c>
       <c r="B47" s="2" t="s">
@@ -11002,37 +10827,37 @@
       </c>
     </row>
     <row r="48" spans="1:2" ht="18.75" customHeight="1">
-      <c r="A48" s="85"/>
+      <c r="A48" s="91"/>
       <c r="B48" s="2" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="18.75" customHeight="1">
-      <c r="A49" s="85"/>
+      <c r="A49" s="91"/>
       <c r="B49" s="2" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="18.75" customHeight="1">
-      <c r="A50" s="85"/>
+      <c r="A50" s="91"/>
       <c r="B50" s="2" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="32.25" customHeight="1">
-      <c r="A51" s="85"/>
+      <c r="A51" s="91"/>
       <c r="B51" s="2" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="27" customHeight="1">
-      <c r="A52" s="85" t="s">
+      <c r="A52" s="91" t="s">
         <v>59</v>
       </c>
-      <c r="B52" s="85"/>
+      <c r="B52" s="91"/>
     </row>
     <row r="53" spans="1:2" ht="30.75" customHeight="1">
-      <c r="A53" s="88" t="s">
+      <c r="A53" s="85" t="s">
         <v>83</v>
       </c>
       <c r="B53" s="2" t="s">
@@ -11040,37 +10865,37 @@
       </c>
     </row>
     <row r="54" spans="1:2" ht="32.25" customHeight="1">
-      <c r="A54" s="89"/>
+      <c r="A54" s="86"/>
       <c r="B54" s="2" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="55" spans="1:2" ht="32.25" customHeight="1">
-      <c r="A55" s="89"/>
+      <c r="A55" s="86"/>
       <c r="B55" s="2" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="56" spans="1:2" ht="32.25" customHeight="1">
-      <c r="A56" s="89"/>
+      <c r="A56" s="86"/>
       <c r="B56" s="2" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="57" spans="1:2" ht="32.25" customHeight="1">
-      <c r="A57" s="90"/>
+      <c r="A57" s="87"/>
       <c r="B57" s="2" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="58" spans="1:2" ht="27" customHeight="1">
-      <c r="A58" s="85" t="s">
+      <c r="A58" s="91" t="s">
         <v>65</v>
       </c>
-      <c r="B58" s="85"/>
+      <c r="B58" s="91"/>
     </row>
     <row r="59" spans="1:2" ht="25.5" customHeight="1">
-      <c r="A59" s="88" t="s">
+      <c r="A59" s="85" t="s">
         <v>88</v>
       </c>
       <c r="B59" s="2" t="s">
@@ -11078,25 +10903,25 @@
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="89"/>
+      <c r="A60" s="86"/>
       <c r="B60" s="2" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" s="90"/>
+      <c r="A61" s="87"/>
       <c r="B61" s="2" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="62" spans="1:2" ht="25.5" customHeight="1">
-      <c r="A62" s="85" t="s">
+      <c r="A62" s="91" t="s">
         <v>87</v>
       </c>
-      <c r="B62" s="85"/>
+      <c r="B62" s="91"/>
     </row>
     <row r="63" spans="1:2" ht="25.5" customHeight="1">
-      <c r="A63" s="85" t="s">
+      <c r="A63" s="91" t="s">
         <v>94</v>
       </c>
       <c r="B63" s="2" t="s">
@@ -11104,31 +10929,31 @@
       </c>
     </row>
     <row r="64" spans="1:2" ht="27">
-      <c r="A64" s="85"/>
+      <c r="A64" s="91"/>
       <c r="B64" s="2" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="65" spans="1:2" ht="18.75" customHeight="1">
-      <c r="A65" s="85"/>
+      <c r="A65" s="91"/>
       <c r="B65" s="2" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="66" spans="1:2" ht="18.75" customHeight="1">
-      <c r="A66" s="85"/>
+      <c r="A66" s="91"/>
       <c r="B66" s="2" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="67" spans="1:2" ht="25.5" customHeight="1">
-      <c r="A67" s="85" t="s">
+      <c r="A67" s="91" t="s">
         <v>93</v>
       </c>
-      <c r="B67" s="85"/>
+      <c r="B67" s="91"/>
     </row>
     <row r="68" spans="1:2" ht="21.75" customHeight="1">
-      <c r="A68" s="85" t="s">
+      <c r="A68" s="91" t="s">
         <v>95</v>
       </c>
       <c r="B68" s="2" t="s">
@@ -11136,37 +10961,37 @@
       </c>
     </row>
     <row r="69" spans="1:2" ht="21.75" customHeight="1">
-      <c r="A69" s="85"/>
+      <c r="A69" s="91"/>
       <c r="B69" s="2" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="70" spans="1:2" ht="21.75" customHeight="1">
-      <c r="A70" s="85"/>
+      <c r="A70" s="91"/>
       <c r="B70" s="2" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="71" spans="1:2" ht="21.75" customHeight="1">
-      <c r="A71" s="85"/>
+      <c r="A71" s="91"/>
       <c r="B71" s="2" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="72" spans="1:2" ht="21.75" customHeight="1">
-      <c r="A72" s="85"/>
+      <c r="A72" s="91"/>
       <c r="B72" s="2" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="73" spans="1:2" ht="25.5" customHeight="1">
-      <c r="A73" s="85" t="s">
+      <c r="A73" s="91" t="s">
         <v>100</v>
       </c>
-      <c r="B73" s="85"/>
+      <c r="B73" s="91"/>
     </row>
     <row r="74" spans="1:2" ht="38.25" customHeight="1">
-      <c r="A74" s="85" t="s">
+      <c r="A74" s="91" t="s">
         <v>101</v>
       </c>
       <c r="B74" s="2" t="s">
@@ -11174,16 +10999,16 @@
       </c>
     </row>
     <row r="75" spans="1:2" ht="28.5" customHeight="1">
-      <c r="A75" s="85"/>
+      <c r="A75" s="91"/>
       <c r="B75" s="2" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="77" spans="1:2" ht="22.5" customHeight="1">
-      <c r="A77" s="86" t="s">
+      <c r="A77" s="88" t="s">
         <v>200</v>
       </c>
-      <c r="B77" s="86"/>
+      <c r="B77" s="88"/>
     </row>
     <row r="78" spans="1:2" ht="22.5" customHeight="1">
       <c r="A78" s="2" t="s">
@@ -11238,21 +11063,21 @@
       </c>
     </row>
     <row r="87" spans="1:3" ht="22.5" customHeight="1">
-      <c r="A87" s="86" t="s">
+      <c r="A87" s="88" t="s">
         <v>169</v>
       </c>
-      <c r="B87" s="86"/>
-      <c r="C87" s="86"/>
+      <c r="B87" s="88"/>
+      <c r="C87" s="88"/>
     </row>
     <row r="88" spans="1:3" ht="22.5" customHeight="1">
-      <c r="A88" s="93" t="s">
+      <c r="A88" s="92" t="s">
         <v>81</v>
       </c>
-      <c r="B88" s="91"/>
-      <c r="C88" s="94"/>
+      <c r="B88" s="90"/>
+      <c r="C88" s="93"/>
     </row>
     <row r="89" spans="1:3" ht="20.25" customHeight="1">
-      <c r="A89" s="88" t="s">
+      <c r="A89" s="85" t="s">
         <v>13</v>
       </c>
       <c r="B89" s="2" t="s">
@@ -11263,7 +11088,7 @@
       </c>
     </row>
     <row r="90" spans="1:3" ht="20.25" customHeight="1">
-      <c r="A90" s="89"/>
+      <c r="A90" s="86"/>
       <c r="B90" s="2" t="s">
         <v>67</v>
       </c>
@@ -11272,7 +11097,7 @@
       </c>
     </row>
     <row r="91" spans="1:3" ht="20.25" customHeight="1">
-      <c r="A91" s="89"/>
+      <c r="A91" s="86"/>
       <c r="B91" s="2" t="s">
         <v>68</v>
       </c>
@@ -11281,7 +11106,7 @@
       </c>
     </row>
     <row r="92" spans="1:3" ht="20.25" customHeight="1">
-      <c r="A92" s="89"/>
+      <c r="A92" s="86"/>
       <c r="B92" s="2" t="s">
         <v>69</v>
       </c>
@@ -11290,7 +11115,7 @@
       </c>
     </row>
     <row r="93" spans="1:3" ht="20.25" customHeight="1">
-      <c r="A93" s="89"/>
+      <c r="A93" s="86"/>
       <c r="B93" s="2" t="s">
         <v>70</v>
       </c>
@@ -11299,7 +11124,7 @@
       </c>
     </row>
     <row r="94" spans="1:3" ht="67.5" customHeight="1">
-      <c r="A94" s="89"/>
+      <c r="A94" s="86"/>
       <c r="B94" s="2" t="s">
         <v>71</v>
       </c>
@@ -11308,7 +11133,7 @@
       </c>
     </row>
     <row r="95" spans="1:3" ht="33" customHeight="1">
-      <c r="A95" s="90"/>
+      <c r="A95" s="87"/>
       <c r="B95" s="2" t="s">
         <v>72</v>
       </c>
@@ -11317,14 +11142,14 @@
       </c>
     </row>
     <row r="96" spans="1:3" ht="27.75" customHeight="1">
-      <c r="A96" s="93" t="s">
+      <c r="A96" s="92" t="s">
         <v>80</v>
       </c>
-      <c r="B96" s="91"/>
-      <c r="C96" s="94"/>
+      <c r="B96" s="90"/>
+      <c r="C96" s="93"/>
     </row>
     <row r="97" spans="1:3" ht="40.5" customHeight="1">
-      <c r="A97" s="88" t="s">
+      <c r="A97" s="85" t="s">
         <v>6</v>
       </c>
       <c r="B97" s="2" t="s">
@@ -11335,7 +11160,7 @@
       </c>
     </row>
     <row r="98" spans="1:3" ht="18" customHeight="1">
-      <c r="A98" s="89"/>
+      <c r="A98" s="86"/>
       <c r="B98" s="2" t="s">
         <v>74</v>
       </c>
@@ -11344,7 +11169,7 @@
       </c>
     </row>
     <row r="99" spans="1:3" ht="67.5">
-      <c r="A99" s="90"/>
+      <c r="A99" s="87"/>
       <c r="B99" s="2" t="s">
         <v>75</v>
       </c>
@@ -11353,21 +11178,21 @@
       </c>
     </row>
     <row r="101" spans="1:3" ht="30.75" customHeight="1">
-      <c r="A101" s="86" t="s">
+      <c r="A101" s="88" t="s">
         <v>170</v>
       </c>
-      <c r="B101" s="86"/>
-      <c r="C101" s="86"/>
+      <c r="B101" s="88"/>
+      <c r="C101" s="88"/>
     </row>
     <row r="102" spans="1:3" ht="23.25" customHeight="1">
-      <c r="A102" s="85" t="s">
+      <c r="A102" s="91" t="s">
         <v>113</v>
       </c>
-      <c r="B102" s="85"/>
-      <c r="C102" s="85"/>
+      <c r="B102" s="91"/>
+      <c r="C102" s="91"/>
     </row>
     <row r="103" spans="1:3" ht="21" customHeight="1">
-      <c r="A103" s="92" t="s">
+      <c r="A103" s="89" t="s">
         <v>104</v>
       </c>
       <c r="B103" s="2" t="s">
@@ -11378,7 +11203,7 @@
       </c>
     </row>
     <row r="104" spans="1:3" ht="29.25" customHeight="1">
-      <c r="A104" s="92"/>
+      <c r="A104" s="89"/>
       <c r="B104" s="2" t="s">
         <v>115</v>
       </c>
@@ -11387,7 +11212,7 @@
       </c>
     </row>
     <row r="105" spans="1:3" ht="24" customHeight="1">
-      <c r="A105" s="92"/>
+      <c r="A105" s="89"/>
       <c r="B105" s="2" t="s">
         <v>116</v>
       </c>
@@ -11396,7 +11221,7 @@
       </c>
     </row>
     <row r="106" spans="1:3" ht="24" customHeight="1">
-      <c r="A106" s="92"/>
+      <c r="A106" s="89"/>
       <c r="B106" s="2" t="s">
         <v>106</v>
       </c>
@@ -11405,7 +11230,7 @@
       </c>
     </row>
     <row r="107" spans="1:3" ht="24" customHeight="1">
-      <c r="A107" s="92"/>
+      <c r="A107" s="89"/>
       <c r="B107" s="2" t="s">
         <v>107</v>
       </c>
@@ -11414,7 +11239,7 @@
       </c>
     </row>
     <row r="108" spans="1:3" ht="24" customHeight="1">
-      <c r="A108" s="92"/>
+      <c r="A108" s="89"/>
       <c r="B108" s="2" t="s">
         <v>108</v>
       </c>
@@ -11423,14 +11248,14 @@
       </c>
     </row>
     <row r="109" spans="1:3" ht="26.25" customHeight="1">
-      <c r="A109" s="85" t="s">
+      <c r="A109" s="91" t="s">
         <v>185</v>
       </c>
-      <c r="B109" s="85"/>
-      <c r="C109" s="85"/>
+      <c r="B109" s="91"/>
+      <c r="C109" s="91"/>
     </row>
     <row r="110" spans="1:3" ht="21.75" customHeight="1">
-      <c r="A110" s="88" t="s">
+      <c r="A110" s="85" t="s">
         <v>118</v>
       </c>
       <c r="B110" s="2" t="s">
@@ -11441,7 +11266,7 @@
       </c>
     </row>
     <row r="111" spans="1:3" ht="24.75" customHeight="1">
-      <c r="A111" s="90"/>
+      <c r="A111" s="87"/>
       <c r="B111" s="2" t="s">
         <v>120</v>
       </c>
@@ -11450,14 +11275,14 @@
       </c>
     </row>
     <row r="112" spans="1:3" ht="28.5" customHeight="1">
-      <c r="A112" s="91" t="s">
+      <c r="A112" s="90" t="s">
         <v>186</v>
       </c>
-      <c r="B112" s="91"/>
-      <c r="C112" s="91"/>
+      <c r="B112" s="90"/>
+      <c r="C112" s="90"/>
     </row>
     <row r="113" spans="1:3" ht="22.5" customHeight="1">
-      <c r="A113" s="85" t="s">
+      <c r="A113" s="91" t="s">
         <v>124</v>
       </c>
       <c r="B113" s="2" t="s">
@@ -11468,7 +11293,7 @@
       </c>
     </row>
     <row r="114" spans="1:3" ht="22.5" customHeight="1">
-      <c r="A114" s="85"/>
+      <c r="A114" s="91"/>
       <c r="B114" s="2" t="s">
         <v>77</v>
       </c>
@@ -11477,7 +11302,7 @@
       </c>
     </row>
     <row r="115" spans="1:3" ht="22.5" customHeight="1">
-      <c r="A115" s="85"/>
+      <c r="A115" s="91"/>
       <c r="B115" s="2" t="s">
         <v>78</v>
       </c>
@@ -11486,7 +11311,7 @@
       </c>
     </row>
     <row r="116" spans="1:3" ht="22.5" customHeight="1">
-      <c r="A116" s="85"/>
+      <c r="A116" s="91"/>
       <c r="B116" s="2" t="s">
         <v>79</v>
       </c>
@@ -11495,14 +11320,14 @@
       </c>
     </row>
     <row r="117" spans="1:3" ht="27" customHeight="1">
-      <c r="A117" s="85" t="s">
+      <c r="A117" s="91" t="s">
         <v>125</v>
       </c>
-      <c r="B117" s="85"/>
-      <c r="C117" s="85"/>
+      <c r="B117" s="91"/>
+      <c r="C117" s="91"/>
     </row>
     <row r="118" spans="1:3" ht="20.25" customHeight="1">
-      <c r="A118" s="88" t="s">
+      <c r="A118" s="85" t="s">
         <v>126</v>
       </c>
       <c r="B118" s="2" t="s">
@@ -11513,7 +11338,7 @@
       </c>
     </row>
     <row r="119" spans="1:3" ht="20.25" customHeight="1">
-      <c r="A119" s="90"/>
+      <c r="A119" s="87"/>
       <c r="B119" s="2" t="s">
         <v>129</v>
       </c>
@@ -11522,14 +11347,14 @@
       </c>
     </row>
     <row r="120" spans="1:3" ht="27" customHeight="1">
-      <c r="A120" s="85" t="s">
+      <c r="A120" s="91" t="s">
         <v>187</v>
       </c>
-      <c r="B120" s="85"/>
-      <c r="C120" s="85"/>
+      <c r="B120" s="91"/>
+      <c r="C120" s="91"/>
     </row>
     <row r="121" spans="1:3" ht="26.25" customHeight="1">
-      <c r="A121" s="88" t="s">
+      <c r="A121" s="85" t="s">
         <v>131</v>
       </c>
       <c r="B121" s="2" t="s">
@@ -11540,7 +11365,7 @@
       </c>
     </row>
     <row r="122" spans="1:3" ht="26.25" customHeight="1">
-      <c r="A122" s="89"/>
+      <c r="A122" s="86"/>
       <c r="B122" s="2" t="s">
         <v>133</v>
       </c>
@@ -11549,7 +11374,7 @@
       </c>
     </row>
     <row r="123" spans="1:3" ht="26.25" customHeight="1">
-      <c r="A123" s="89"/>
+      <c r="A123" s="86"/>
       <c r="B123" s="2" t="s">
         <v>134</v>
       </c>
@@ -11558,7 +11383,7 @@
       </c>
     </row>
     <row r="124" spans="1:3" ht="26.25" customHeight="1">
-      <c r="A124" s="89"/>
+      <c r="A124" s="86"/>
       <c r="B124" s="2" t="s">
         <v>135</v>
       </c>
@@ -11567,7 +11392,7 @@
       </c>
     </row>
     <row r="125" spans="1:3" ht="26.25" customHeight="1">
-      <c r="A125" s="89"/>
+      <c r="A125" s="86"/>
       <c r="B125" s="2" t="s">
         <v>136</v>
       </c>
@@ -11576,7 +11401,7 @@
       </c>
     </row>
     <row r="126" spans="1:3" ht="26.25" customHeight="1">
-      <c r="A126" s="89"/>
+      <c r="A126" s="86"/>
       <c r="B126" s="2" t="s">
         <v>137</v>
       </c>
@@ -11585,7 +11410,7 @@
       </c>
     </row>
     <row r="127" spans="1:3" ht="26.25" customHeight="1">
-      <c r="A127" s="89"/>
+      <c r="A127" s="86"/>
       <c r="B127" s="2" t="s">
         <v>138</v>
       </c>
@@ -11594,7 +11419,7 @@
       </c>
     </row>
     <row r="128" spans="1:3" ht="26.25" customHeight="1">
-      <c r="A128" s="89"/>
+      <c r="A128" s="86"/>
       <c r="B128" s="2" t="s">
         <v>139</v>
       </c>
@@ -11603,7 +11428,7 @@
       </c>
     </row>
     <row r="129" spans="1:3" ht="26.25" customHeight="1">
-      <c r="A129" s="89"/>
+      <c r="A129" s="86"/>
       <c r="B129" s="2" t="s">
         <v>140</v>
       </c>
@@ -11612,7 +11437,7 @@
       </c>
     </row>
     <row r="130" spans="1:3" ht="26.25" customHeight="1">
-      <c r="A130" s="89"/>
+      <c r="A130" s="86"/>
       <c r="B130" s="2" t="s">
         <v>141</v>
       </c>
@@ -11621,7 +11446,7 @@
       </c>
     </row>
     <row r="131" spans="1:3" ht="26.25" customHeight="1">
-      <c r="A131" s="90"/>
+      <c r="A131" s="87"/>
       <c r="B131" s="2" t="s">
         <v>142</v>
       </c>
@@ -11630,21 +11455,21 @@
       </c>
     </row>
     <row r="133" spans="1:3" ht="30.75" customHeight="1">
-      <c r="A133" s="86" t="s">
+      <c r="A133" s="88" t="s">
         <v>171</v>
       </c>
-      <c r="B133" s="86"/>
-      <c r="C133" s="86"/>
+      <c r="B133" s="88"/>
+      <c r="C133" s="88"/>
     </row>
     <row r="134" spans="1:3" ht="23.25" customHeight="1">
-      <c r="A134" s="85" t="s">
+      <c r="A134" s="91" t="s">
         <v>174</v>
       </c>
-      <c r="B134" s="85"/>
-      <c r="C134" s="85"/>
+      <c r="B134" s="91"/>
+      <c r="C134" s="91"/>
     </row>
     <row r="135" spans="1:3" ht="21" customHeight="1">
-      <c r="A135" s="92" t="s">
+      <c r="A135" s="89" t="s">
         <v>177</v>
       </c>
       <c r="B135" s="2" t="s">
@@ -11655,7 +11480,7 @@
       </c>
     </row>
     <row r="136" spans="1:3" ht="29.25" customHeight="1">
-      <c r="A136" s="92"/>
+      <c r="A136" s="89"/>
       <c r="B136" s="2" t="s">
         <v>176</v>
       </c>
@@ -11664,14 +11489,14 @@
       </c>
     </row>
     <row r="137" spans="1:3" ht="26.25" customHeight="1">
-      <c r="A137" s="85" t="s">
+      <c r="A137" s="91" t="s">
         <v>172</v>
       </c>
-      <c r="B137" s="85"/>
-      <c r="C137" s="85"/>
+      <c r="B137" s="91"/>
+      <c r="C137" s="91"/>
     </row>
     <row r="138" spans="1:3" ht="21.75" customHeight="1">
-      <c r="A138" s="92" t="s">
+      <c r="A138" s="89" t="s">
         <v>178</v>
       </c>
       <c r="B138" s="2" t="s">
@@ -11682,7 +11507,7 @@
       </c>
     </row>
     <row r="139" spans="1:3" ht="49.5" customHeight="1">
-      <c r="A139" s="92"/>
+      <c r="A139" s="89"/>
       <c r="B139" s="2" t="s">
         <v>183</v>
       </c>
@@ -11691,14 +11516,14 @@
       </c>
     </row>
     <row r="140" spans="1:3" ht="28.5" customHeight="1">
-      <c r="A140" s="91" t="s">
+      <c r="A140" s="90" t="s">
         <v>173</v>
       </c>
-      <c r="B140" s="91"/>
-      <c r="C140" s="91"/>
+      <c r="B140" s="90"/>
+      <c r="C140" s="90"/>
     </row>
     <row r="141" spans="1:3" ht="21" customHeight="1">
-      <c r="A141" s="92" t="s">
+      <c r="A141" s="89" t="s">
         <v>180</v>
       </c>
       <c r="B141" s="2" t="s">
@@ -11709,7 +11534,7 @@
       </c>
     </row>
     <row r="142" spans="1:3" ht="29.25" customHeight="1">
-      <c r="A142" s="92"/>
+      <c r="A142" s="89"/>
       <c r="B142" s="2" t="s">
         <v>176</v>
       </c>
@@ -11719,15 +11544,28 @@
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="A97:A99"/>
-    <mergeCell ref="A101:C101"/>
-    <mergeCell ref="A141:A142"/>
-    <mergeCell ref="A138:A139"/>
-    <mergeCell ref="A140:C140"/>
-    <mergeCell ref="A133:C133"/>
-    <mergeCell ref="A134:C134"/>
-    <mergeCell ref="A135:A136"/>
-    <mergeCell ref="A137:C137"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A26:A34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A36:A38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A12:A24"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A40:A43"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="A68:A72"/>
+    <mergeCell ref="A53:A57"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="A59:A61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="A47:A51"/>
+    <mergeCell ref="A52:B52"/>
     <mergeCell ref="A63:A66"/>
     <mergeCell ref="A67:B67"/>
     <mergeCell ref="A120:C120"/>
@@ -11744,28 +11582,15 @@
     <mergeCell ref="A88:C88"/>
     <mergeCell ref="A89:A95"/>
     <mergeCell ref="A96:C96"/>
-    <mergeCell ref="A53:A57"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="A59:A61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="A47:A51"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A26:A34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A36:A38"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A12:A24"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A40:A43"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="A68:A72"/>
+    <mergeCell ref="A97:A99"/>
+    <mergeCell ref="A101:C101"/>
+    <mergeCell ref="A141:A142"/>
+    <mergeCell ref="A138:A139"/>
+    <mergeCell ref="A140:C140"/>
+    <mergeCell ref="A133:C133"/>
+    <mergeCell ref="A134:C134"/>
+    <mergeCell ref="A135:A136"/>
+    <mergeCell ref="A137:C137"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
